--- a/assets/samples/fitness_centers/bucuresti/cards_sample_50.xlsx
+++ b/assets/samples/fitness_centers/bucuresti/cards_sample_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="641">
   <si>
     <t>entity_id</t>
   </si>
@@ -79,18 +79,6 @@
     <t>tiktok</t>
   </si>
   <si>
-    <t>LDI1-RO-FI-BK8Y-25FQ-33</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-7Z38-06G3-66</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-5W5F-ZPVQ-63</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-1X8P-X9W4-41</t>
-  </si>
-  <si>
     <t>LDI1-RO-FI-F6EC-5EQN-67</t>
   </si>
   <si>
@@ -106,42 +94,6 @@
     <t>LDI1-RO-FI-17GW-CTWX-75</t>
   </si>
   <si>
-    <t>LDI1-RO-FI-94V2-2S9M-04</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-1FE3-FZ3X-66</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-WYNQ-V68K-64</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-1DBF-1KY4-38</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-1A7H-8P41-11</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-173S-81VY-82</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-1HM8-GAT0-01</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-F2MB-MXH8-04</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-1P6R-JNVN-85</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-10FH-EPXA-69</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-12P4-77J4-74</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-1598-Q7WZ-14</t>
-  </si>
-  <si>
     <t>LDI1-RO-FI-1DHG-ZT75-39</t>
   </si>
   <si>
@@ -163,15 +115,6 @@
     <t>LDI1-RO-FI-1N9S-7V5C-21</t>
   </si>
   <si>
-    <t>LDI1-RO-FI-CX16-0B20-93</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-T8QS-S004-76</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-1DRH-5BRX-15</t>
-  </si>
-  <si>
     <t>LDI1-RO-FI-1K3J-EYHB-91</t>
   </si>
   <si>
@@ -184,61 +127,106 @@
     <t>LDI1-RO-FI-13HV-QEFM-08</t>
   </si>
   <si>
-    <t>LDI1-RO-FI-QK5E-A924-54</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-15E0-ZRYN-51</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-SXYG-XM1Y-02</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-DB1M-RMFB-62</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-155S-S8M5-27</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-9ATT-V0PM-36</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-YQ7A-XVP0-13</t>
-  </si>
-  <si>
     <t>LDI1-RO-FI-G6J3-E1XE-30</t>
   </si>
   <si>
     <t>LDI1-RO-FI-16TW-ENPS-02</t>
   </si>
   <si>
-    <t>LDI1-RO-FI-JGYE-AD20-60</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-1VCX-R6Q0-13</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-GCW1-BZCY-40</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-1DSC-VK1Q-40</t>
-  </si>
-  <si>
-    <t>LDI1-RO-FI-5G2P-PD2C-03</t>
-  </si>
-  <si>
     <t>LDI1-RO-FI-BD3X-5B3D-50</t>
   </si>
   <si>
-    <t>Fitness 4 All Hunedoara</t>
-  </si>
-  <si>
-    <t>Elite Center Hunedoara</t>
-  </si>
-  <si>
-    <t>Fitness World Studio</t>
-  </si>
-  <si>
-    <t>Grand Fitness</t>
+    <t>LDI1-RO-FI-7HSR-6RBK-83</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-1CA3-3836-95</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-1GH2-S1K8-30</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-TRK7-9QQH-22</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-17B9-M93T-07</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-RZFA-G6GN-36</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-1B0B-3YCT-08</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-11S5-KH5Z-18</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-KNM1-ZRDK-69</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-5SAS-RKCY-28</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-1DAM-NS3K-54</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-M4P8-DGCT-93</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-1KHK-CK5Y-31</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-7GG6-73MZ-11</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-1JM2-83AG-16</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-HB05-7BJY-49</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-1XY5-T0HW-36</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-1DQT-KTG5-31</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-YB0T-6N8J-81</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-144K-VH00-65</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-10RR-GB48-34</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-BFXP-EGAH-47</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-RQD9-M78D-19</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-V016-SSGC-57</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-12Z8-31EK-00</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-1EQS-W2DQ-87</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-1MFX-B6TA-59</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-5H4B-TMBQ-66</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-VAY0-HAYM-15</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-1KAZ-0J3W-38</t>
+  </si>
+  <si>
+    <t>LDI1-RO-FI-18JQ-ZS3N-68</t>
   </si>
   <si>
     <t>Sas Gym</t>
@@ -256,42 +244,6 @@
     <t>Phoenix Gym</t>
   </si>
   <si>
-    <t>BEFIT Magnolia</t>
-  </si>
-  <si>
-    <t>Get Fit</t>
-  </si>
-  <si>
-    <t>FIT4U Primariei</t>
-  </si>
-  <si>
-    <t>Oxygen Gym Nufaru</t>
-  </si>
-  <si>
-    <t>Dynamic Oradea</t>
-  </si>
-  <si>
-    <t>SmartFit Studio Arad</t>
-  </si>
-  <si>
-    <t>CLASSIC GYM ARAD</t>
-  </si>
-  <si>
-    <t>Rock Fit Studio Arad</t>
-  </si>
-  <si>
-    <t>Stay Fit Gym Afi Arad</t>
-  </si>
-  <si>
-    <t>Stay Fit Gym Vladimirescu Arad</t>
-  </si>
-  <si>
-    <t>Tim Gym</t>
-  </si>
-  <si>
-    <t>The Rock Gym</t>
-  </si>
-  <si>
     <t>Alexandreea Club Fitness &amp; Spa | Piscină, Fitness, Aerobic,Teren Fotbal, Spinning | Initiere Inot Copii &amp; Adulti</t>
   </si>
   <si>
@@ -313,15 +265,6 @@
     <t>Sala Fitness Floreasca GYM - Dorobanti</t>
   </si>
   <si>
-    <t>Saba Gym</t>
-  </si>
-  <si>
-    <t>Sală de fitness Gladiator</t>
-  </si>
-  <si>
-    <t>Athletic Sport Center</t>
-  </si>
-  <si>
     <t>Fresh Club - Sala Aerobic si Fitness Bucuresti</t>
   </si>
   <si>
@@ -334,67 +277,109 @@
     <t>Elite Gym</t>
   </si>
   <si>
-    <t>Friend's Arena S.R.L.</t>
-  </si>
-  <si>
-    <t>Gym One 2</t>
-  </si>
-  <si>
-    <t>Gym One 5</t>
-  </si>
-  <si>
-    <t>Fit4Life Gym</t>
-  </si>
-  <si>
-    <t>Haltere Club Timișoara</t>
-  </si>
-  <si>
-    <t>MY GYM</t>
-  </si>
-  <si>
-    <t>Extreme</t>
-  </si>
-  <si>
     <t>Sweat - The Light</t>
   </si>
   <si>
     <t>Sweat - Promenada - Zone 313</t>
   </si>
   <si>
-    <t>Studio C</t>
-  </si>
-  <si>
-    <t>Area Gym - Brasov - Unirea</t>
-  </si>
-  <si>
-    <t>18GYM Unirea Mall Brasov</t>
-  </si>
-  <si>
-    <t>Abc</t>
-  </si>
-  <si>
-    <t>Fitfinity Gym Endorfine</t>
-  </si>
-  <si>
     <t>SHAPE UP STUDIO UNIRII</t>
   </si>
   <si>
+    <t>FITACTIVE București Vitan</t>
+  </si>
+  <si>
+    <t>Gym Life</t>
+  </si>
+  <si>
+    <t>Anturaj Fitness</t>
+  </si>
+  <si>
+    <t>Onyx Fitness Club - Sala Fitness Aerobic</t>
+  </si>
+  <si>
+    <t>Club Elite</t>
+  </si>
+  <si>
+    <t>Absolute Gym</t>
+  </si>
+  <si>
+    <t>Downtown Fitness Vitan</t>
+  </si>
+  <si>
+    <t>Stay Fit</t>
+  </si>
+  <si>
+    <t>World Class București București Mall</t>
+  </si>
+  <si>
+    <t>Stay Fit Gym - Pipera</t>
+  </si>
+  <si>
+    <t>Uni Sports Cotroceni</t>
+  </si>
+  <si>
+    <t>Fitness Academy Rahova</t>
+  </si>
+  <si>
+    <t>Human Fitness</t>
+  </si>
+  <si>
+    <t>LadyFIT</t>
+  </si>
+  <si>
+    <t>FitClass Club</t>
+  </si>
+  <si>
+    <t>Downtown Fitness Obor</t>
+  </si>
+  <si>
+    <t>Downtown Fitness &amp; SPA Matei Basarab</t>
+  </si>
+  <si>
+    <t>Downtown Fitness Mihalache</t>
+  </si>
+  <si>
+    <t>Enjoy Fitness club (fost Animal Kingdom)</t>
+  </si>
+  <si>
+    <t>Groove BOX</t>
+  </si>
+  <si>
+    <t>Uzina</t>
+  </si>
+  <si>
+    <t>CrossFit Unbroken Spirit</t>
+  </si>
+  <si>
+    <t>Stay Fit Gym Liberty</t>
+  </si>
+  <si>
+    <t>Jungle Gym Bucuresti</t>
+  </si>
+  <si>
+    <t>BODYFIT</t>
+  </si>
+  <si>
+    <t>Royal Fitness Club</t>
+  </si>
+  <si>
+    <t>Best Fitness Gym</t>
+  </si>
+  <si>
+    <t>700 Fit Club</t>
+  </si>
+  <si>
+    <t>700 Fit Club - Drumul Taberei</t>
+  </si>
+  <si>
+    <t>New Fit Way</t>
+  </si>
+  <si>
     <t>Sală de fitness</t>
   </si>
   <si>
-    <t>Complex sportiv</t>
-  </si>
-  <si>
-    <t>Bulevardul Dacia, Hunedoara</t>
-  </si>
-  <si>
-    <t>Blocul 5, Strada Victoriei 17, Hunedoara</t>
-  </si>
-  <si>
-    <t>Strada George Enescu 17, Hunedoara</t>
-  </si>
-  <si>
-    <t>Strada 13 Decembrie 96, Brașov</t>
+    <t>Club de gimnastică</t>
   </si>
   <si>
     <t>Strada Traian Popovici 79-91, București</t>
@@ -412,42 +397,6 @@
     <t>Strada Vasile Lascăr 105, București</t>
   </si>
   <si>
-    <t>Strada Transilvaniei 18, Oradea</t>
-  </si>
-  <si>
-    <t>Str. Nufărului 28E, Oradea</t>
-  </si>
-  <si>
-    <t>Strada Primăriei 29, nr, Oradea</t>
-  </si>
-  <si>
-    <t>Str. Ogorului 63A, Oradea</t>
-  </si>
-  <si>
-    <t>Strada Alexandru Vaida Voievod 18, Oradea</t>
-  </si>
-  <si>
-    <t>Bulevardul Revoluției 39-41, Arad</t>
-  </si>
-  <si>
-    <t>în curtea interioara a imobilului, Bulevardul Revoluției 78, Km 0, Arad</t>
-  </si>
-  <si>
-    <t>Strada Petru Rareș 4, Arad</t>
-  </si>
-  <si>
-    <t>Calea Aurel Vlaicu 14, Arad</t>
-  </si>
-  <si>
-    <t>Str. Cetății Orod, Vladimirescu</t>
-  </si>
-  <si>
-    <t>Strada Arh. Berechet nr.1, etaj 3, Câmpulung</t>
-  </si>
-  <si>
-    <t>Strada Otilia Cazimir 10, Iași</t>
-  </si>
-  <si>
     <t>Bulevardul Basarabia 37-39, București</t>
   </si>
   <si>
@@ -469,15 +418,6 @@
     <t>Strada Frederic Chopin 12, București</t>
   </si>
   <si>
-    <t>Strada Polonă 12 i, Otopeni</t>
-  </si>
-  <si>
-    <t>Strada 9 Mai 57, Sighetu Marmației</t>
-  </si>
-  <si>
-    <t>Strada Constantin Brâncuși 148-152, Cluj-Napoca</t>
-  </si>
-  <si>
     <t>Strada Anastasie Panu 50, București</t>
   </si>
   <si>
@@ -490,61 +430,106 @@
     <t>Strada Theodor D. Speranția 14, București</t>
   </si>
   <si>
-    <t>Str. Lacului, 1, Timișoara, Timis, Strada Lacului 1, 300425</t>
-  </si>
-  <si>
-    <t>Str. Mureș 116A, Timișoara</t>
-  </si>
-  <si>
-    <t>DN59 8, Timișoara</t>
-  </si>
-  <si>
-    <t>Calea Torontalului 53, Timișoara</t>
-  </si>
-  <si>
-    <t>Strada Amforei 1, Timișoara</t>
-  </si>
-  <si>
-    <t>Șos. București-Domnești 16</t>
-  </si>
-  <si>
-    <t>Strada Soldat Ghiță Șerban 15, București</t>
-  </si>
-  <si>
     <t>Bulevardul Iuliu Maniu 6Q, București</t>
   </si>
   <si>
     <t>Str. Barbu Văcărescu 313-315, București</t>
   </si>
   <si>
-    <t>Str. Nicolae Titulescu 2, Brașov</t>
-  </si>
-  <si>
-    <t>Unirea Shopping Center, Bulevardul Gării 3A, Etajul 2, Brașov</t>
-  </si>
-  <si>
-    <t>Unirea Shopping Center, Bulevardul Gării 3A, etajul 3, Brașov</t>
-  </si>
-  <si>
-    <t>Calea Fălticeni, Cumpărătura</t>
-  </si>
-  <si>
-    <t>Strada Hack Halasi Gyula 85, Oradea</t>
-  </si>
-  <si>
     <t>Bloc C1, Strada Mămulari 2, blC1, sc 2, parter, București</t>
   </si>
   <si>
-    <t>331013</t>
-  </si>
-  <si>
-    <t>331071</t>
-  </si>
-  <si>
-    <t>331056</t>
-  </si>
-  <si>
-    <t>500164</t>
+    <t>Calea Vitan 289, București</t>
+  </si>
+  <si>
+    <t>Drumul Gura Caliței 159, București</t>
+  </si>
+  <si>
+    <t>Șoseaua Olteniței 31, București</t>
+  </si>
+  <si>
+    <t>Soseaua de Centura 5A, București</t>
+  </si>
+  <si>
+    <t>Str. Școlii, Voluntari</t>
+  </si>
+  <si>
+    <t>Strada Antiaeriană 65, București</t>
+  </si>
+  <si>
+    <t>Calea Vitan 13-19, București</t>
+  </si>
+  <si>
+    <t>Strada Răcari 57, București</t>
+  </si>
+  <si>
+    <t>Calea Vitan 55-59, București</t>
+  </si>
+  <si>
+    <t>14, Bulevardul Dimitrie Pompeiu 9-9A, București</t>
+  </si>
+  <si>
+    <t>Str. Sergent Nuțu Ion 8-10, București</t>
+  </si>
+  <si>
+    <t>Calea Rahovei 201, București</t>
+  </si>
+  <si>
+    <t>Bloc G1, Bulevardul Unirii 65, tronson 4, mezanin, București</t>
+  </si>
+  <si>
+    <t>Bulevardul Chișinău 1, Nr, București</t>
+  </si>
+  <si>
+    <t>Strada Bărăției 35 Parter, București</t>
+  </si>
+  <si>
+    <t>Strada Rotundă 6A, București</t>
+  </si>
+  <si>
+    <t>Aleea Câmpul Moşilor, București</t>
+  </si>
+  <si>
+    <t>Strada Matei Basarab 97, București</t>
+  </si>
+  <si>
+    <t>Bulevardul Ion Mihalache 60, București</t>
+  </si>
+  <si>
+    <t>Strada Bucur 7, București</t>
+  </si>
+  <si>
+    <t>Calea Rahovei 198, Calea Rahovei 196, București</t>
+  </si>
+  <si>
+    <t>Splaiul Unirii nr. 160, București</t>
+  </si>
+  <si>
+    <t>Splaiul Unirii 257-259, București</t>
+  </si>
+  <si>
+    <t>Strada Progresului 151-171, București</t>
+  </si>
+  <si>
+    <t>Strada Huedin 19, București</t>
+  </si>
+  <si>
+    <t>Strada Comandor Eugen Botez nr 40, București</t>
+  </si>
+  <si>
+    <t>Bulevardul Iuliu Maniu 78-92, București</t>
+  </si>
+  <si>
+    <t>Strada Valea Oltului 199-201, București</t>
+  </si>
+  <si>
+    <t>83 Horia Macelǎriu Street, București</t>
+  </si>
+  <si>
+    <t>Str. Brașov 25, București</t>
+  </si>
+  <si>
+    <t>Strada Mașina de Pâine 49-51, București</t>
   </si>
   <si>
     <t>030777</t>
@@ -559,42 +544,6 @@
     <t>020495</t>
   </si>
   <si>
-    <t>410412</t>
-  </si>
-  <si>
-    <t>410583</t>
-  </si>
-  <si>
-    <t>410209</t>
-  </si>
-  <si>
-    <t>410554</t>
-  </si>
-  <si>
-    <t>410088</t>
-  </si>
-  <si>
-    <t>310181</t>
-  </si>
-  <si>
-    <t>310025</t>
-  </si>
-  <si>
-    <t>310210</t>
-  </si>
-  <si>
-    <t>310159</t>
-  </si>
-  <si>
-    <t>317405</t>
-  </si>
-  <si>
-    <t>115100</t>
-  </si>
-  <si>
-    <t>700400</t>
-  </si>
-  <si>
     <t>022114</t>
   </si>
   <si>
@@ -616,15 +565,6 @@
     <t>014192</t>
   </si>
   <si>
-    <t>075100</t>
-  </si>
-  <si>
-    <t>435500</t>
-  </si>
-  <si>
-    <t>400458</t>
-  </si>
-  <si>
     <t>031166</t>
   </si>
   <si>
@@ -634,114 +574,84 @@
     <t>031083</t>
   </si>
   <si>
-    <t>300472</t>
-  </si>
-  <si>
-    <t>300763</t>
-  </si>
-  <si>
-    <t>300254</t>
-  </si>
-  <si>
-    <t>300668</t>
-  </si>
-  <si>
-    <t>300671</t>
-  </si>
-  <si>
-    <t>077090</t>
-  </si>
-  <si>
-    <t>515100</t>
-  </si>
-  <si>
     <t>061344</t>
   </si>
   <si>
     <t>077190</t>
   </si>
   <si>
-    <t>500100</t>
-  </si>
-  <si>
-    <t>500148</t>
-  </si>
-  <si>
-    <t>727046</t>
-  </si>
-  <si>
-    <t>417498</t>
-  </si>
-  <si>
-    <t>Hunedoara</t>
-  </si>
-  <si>
-    <t>Brașov</t>
+    <t>077160</t>
+  </si>
+  <si>
+    <t>032604</t>
+  </si>
+  <si>
+    <t>041315</t>
+  </si>
+  <si>
+    <t>077120</t>
+  </si>
+  <si>
+    <t>051079</t>
+  </si>
+  <si>
+    <t>031733</t>
+  </si>
+  <si>
+    <t>031827</t>
+  </si>
+  <si>
+    <t>031282</t>
+  </si>
+  <si>
+    <t>020335</t>
+  </si>
+  <si>
+    <t>050762</t>
+  </si>
+  <si>
+    <t>050909</t>
+  </si>
+  <si>
+    <t>030829</t>
+  </si>
+  <si>
+    <t>022141</t>
+  </si>
+  <si>
+    <t>030197</t>
+  </si>
+  <si>
+    <t>021202</t>
+  </si>
+  <si>
+    <t>011174</t>
+  </si>
+  <si>
+    <t>050908</t>
+  </si>
+  <si>
+    <t>040041</t>
+  </si>
+  <si>
+    <t>030137</t>
+  </si>
+  <si>
+    <t>020491</t>
+  </si>
+  <si>
+    <t>061111</t>
+  </si>
+  <si>
+    <t>061444</t>
+  </si>
+  <si>
+    <t>051734</t>
   </si>
   <si>
     <t>București</t>
   </si>
   <si>
-    <t>Bihor</t>
-  </si>
-  <si>
-    <t>Arad</t>
-  </si>
-  <si>
-    <t>Argeș</t>
-  </si>
-  <si>
-    <t>Iași</t>
-  </si>
-  <si>
-    <t>Ilfov</t>
-  </si>
-  <si>
-    <t>Maramureș</t>
-  </si>
-  <si>
-    <t>Cluj</t>
-  </si>
-  <si>
-    <t>Timiș</t>
-  </si>
-  <si>
-    <t>Suceava</t>
-  </si>
-  <si>
-    <t>Oradea</t>
-  </si>
-  <si>
-    <t>Câmpulung</t>
-  </si>
-  <si>
-    <t>Otopeni</t>
-  </si>
-  <si>
-    <t>Sighetu Marmației</t>
-  </si>
-  <si>
-    <t>Cluj-Napoca</t>
-  </si>
-  <si>
-    <t>Timișoara</t>
-  </si>
-  <si>
-    <t>Domnești</t>
-  </si>
-  <si>
-    <t>45.7593955</t>
-  </si>
-  <si>
-    <t>45.7512288</t>
-  </si>
-  <si>
-    <t>45.7538679</t>
-  </si>
-  <si>
-    <t>45.6796782</t>
-  </si>
-  <si>
     <t>44.4222366</t>
   </si>
   <si>
@@ -757,42 +667,6 @@
     <t>44.4451266</t>
   </si>
   <si>
-    <t>47.0777171</t>
-  </si>
-  <si>
-    <t>47.0369936</t>
-  </si>
-  <si>
-    <t>47.0569</t>
-  </si>
-  <si>
-    <t>47.0284461</t>
-  </si>
-  <si>
-    <t>47.0475755</t>
-  </si>
-  <si>
-    <t>46.1796527</t>
-  </si>
-  <si>
-    <t>46.1752618</t>
-  </si>
-  <si>
-    <t>46.1884859</t>
-  </si>
-  <si>
-    <t>46.1905816</t>
-  </si>
-  <si>
-    <t>46.1669616</t>
-  </si>
-  <si>
-    <t>45.2696367</t>
-  </si>
-  <si>
-    <t>47.1590905</t>
-  </si>
-  <si>
     <t>44.433388</t>
   </si>
   <si>
@@ -814,15 +688,6 @@
     <t>44.4621476</t>
   </si>
   <si>
-    <t>44.5462088</t>
-  </si>
-  <si>
-    <t>47.9276157</t>
-  </si>
-  <si>
-    <t>46.7604077</t>
-  </si>
-  <si>
     <t>44.4163447</t>
   </si>
   <si>
@@ -835,58 +700,106 @@
     <t>44.4246115</t>
   </si>
   <si>
-    <t>45.7348408</t>
-  </si>
-  <si>
-    <t>45.728441</t>
-  </si>
-  <si>
-    <t>45.757149</t>
-  </si>
-  <si>
-    <t>45.772103</t>
-  </si>
-  <si>
-    <t>45.7618612</t>
-  </si>
-  <si>
-    <t>44.4031801</t>
-  </si>
-  <si>
-    <t>44.415376</t>
-  </si>
-  <si>
     <t>44.4347598</t>
   </si>
   <si>
     <t>44.4766311</t>
   </si>
   <si>
-    <t>45.6478786</t>
-  </si>
-  <si>
-    <t>45.6611188</t>
-  </si>
-  <si>
-    <t>47.5697137</t>
-  </si>
-  <si>
-    <t>47.0221332</t>
-  </si>
-  <si>
     <t>44.428577</t>
   </si>
   <si>
-    <t>22.9081019</t>
-  </si>
-  <si>
-    <t>22.9048309</t>
-  </si>
-  <si>
-    <t>22.9100183</t>
-  </si>
-  <si>
-    <t>25.6147359</t>
+    <t>44.4057611</t>
+  </si>
+  <si>
+    <t>44.4197561</t>
+  </si>
+  <si>
+    <t>44.3978336</t>
+  </si>
+  <si>
+    <t>44.338842</t>
+  </si>
+  <si>
+    <t>44.4901857</t>
+  </si>
+  <si>
+    <t>44.4109937</t>
+  </si>
+  <si>
+    <t>44.4230563</t>
+  </si>
+  <si>
+    <t>44.413194</t>
+  </si>
+  <si>
+    <t>44.4210354</t>
+  </si>
+  <si>
+    <t>44.4846143</t>
+  </si>
+  <si>
+    <t>44.424293</t>
+  </si>
+  <si>
+    <t>44.4169382</t>
+  </si>
+  <si>
+    <t>44.4263083</t>
+  </si>
+  <si>
+    <t>44.445146</t>
+  </si>
+  <si>
+    <t>44.4303977</t>
+  </si>
+  <si>
+    <t>44.415647</t>
+  </si>
+  <si>
+    <t>44.4502806</t>
+  </si>
+  <si>
+    <t>44.4313552</t>
+  </si>
+  <si>
+    <t>44.4586368</t>
+  </si>
+  <si>
+    <t>44.4212284</t>
+  </si>
+  <si>
+    <t>44.4193026</t>
+  </si>
+  <si>
+    <t>44.4116403</t>
+  </si>
+  <si>
+    <t>44.408234</t>
+  </si>
+  <si>
+    <t>44.414964</t>
+  </si>
+  <si>
+    <t>44.3842981</t>
+  </si>
+  <si>
+    <t>44.4600394</t>
+  </si>
+  <si>
+    <t>44.4344494</t>
+  </si>
+  <si>
+    <t>44.4238835</t>
+  </si>
+  <si>
+    <t>44.4902411</t>
+  </si>
+  <si>
+    <t>44.4170484</t>
+  </si>
+  <si>
+    <t>44.4556808</t>
   </si>
   <si>
     <t>26.1335111</t>
@@ -904,42 +817,6 @@
     <t>26.1109722</t>
   </si>
   <si>
-    <t>21.916341</t>
-  </si>
-  <si>
-    <t>21.948661</t>
-  </si>
-  <si>
-    <t>21.9220657</t>
-  </si>
-  <si>
-    <t>21.9606208</t>
-  </si>
-  <si>
-    <t>21.9262121</t>
-  </si>
-  <si>
-    <t>21.3220356</t>
-  </si>
-  <si>
-    <t>21.3176014</t>
-  </si>
-  <si>
-    <t>21.3289526</t>
-  </si>
-  <si>
-    <t>21.3187622</t>
-  </si>
-  <si>
-    <t>21.3876604</t>
-  </si>
-  <si>
-    <t>25.0432155</t>
-  </si>
-  <si>
-    <t>27.5969389</t>
-  </si>
-  <si>
     <t>26.1493624</t>
   </si>
   <si>
@@ -961,15 +838,6 @@
     <t>26.1059935</t>
   </si>
   <si>
-    <t>26.072956</t>
-  </si>
-  <si>
-    <t>23.8991475</t>
-  </si>
-  <si>
-    <t>23.6134888</t>
-  </si>
-  <si>
     <t>26.1207801</t>
   </si>
   <si>
@@ -982,55 +850,106 @@
     <t>26.1241463</t>
   </si>
   <si>
-    <t>21.1979777</t>
-  </si>
-  <si>
-    <t>21.2333851</t>
-  </si>
-  <si>
-    <t>21.2180043</t>
-  </si>
-  <si>
-    <t>21.21652</t>
-  </si>
-  <si>
-    <t>21.2184097</t>
-  </si>
-  <si>
-    <t>25.9540021</t>
-  </si>
-  <si>
-    <t>26.1692759</t>
-  </si>
-  <si>
     <t>26.0506442</t>
   </si>
   <si>
     <t>26.106114</t>
   </si>
   <si>
-    <t>25.606302</t>
-  </si>
-  <si>
-    <t>25.6105991</t>
-  </si>
-  <si>
-    <t>26.2749884</t>
-  </si>
-  <si>
-    <t>21.9238989</t>
-  </si>
-  <si>
     <t>26.1076559</t>
   </si>
   <si>
-    <t>https://www.fitnesshunedoara.ro/</t>
-  </si>
-  <si>
-    <t>https://hdfitness.ro/</t>
-  </si>
-  <si>
-    <t>https://www.grand-fitness.ro/</t>
+    <t>26.1424972</t>
+  </si>
+  <si>
+    <t>26.1998143</t>
+  </si>
+  <si>
+    <t>26.1114818</t>
+  </si>
+  <si>
+    <t>26.094125</t>
+  </si>
+  <si>
+    <t>26.2006478</t>
+  </si>
+  <si>
+    <t>26.0551191</t>
+  </si>
+  <si>
+    <t>26.1243049</t>
+  </si>
+  <si>
+    <t>26.1382356</t>
+  </si>
+  <si>
+    <t>26.1272093</t>
+  </si>
+  <si>
+    <t>26.1196758</t>
+  </si>
+  <si>
+    <t>26.064029</t>
+  </si>
+  <si>
+    <t>26.0811803</t>
+  </si>
+  <si>
+    <t>26.1237868</t>
+  </si>
+  <si>
+    <t>26.1575</t>
+  </si>
+  <si>
+    <t>26.1049864</t>
+  </si>
+  <si>
+    <t>26.160987</t>
+  </si>
+  <si>
+    <t>26.1276169</t>
+  </si>
+  <si>
+    <t>26.1287753</t>
+  </si>
+  <si>
+    <t>26.0774563</t>
+  </si>
+  <si>
+    <t>26.1072313</t>
+  </si>
+  <si>
+    <t>26.0809958</t>
+  </si>
+  <si>
+    <t>26.1180163</t>
+  </si>
+  <si>
+    <t>26.126472</t>
+  </si>
+  <si>
+    <t>26.0806565</t>
+  </si>
+  <si>
+    <t>26.1017181</t>
+  </si>
+  <si>
+    <t>26.1049808</t>
+  </si>
+  <si>
+    <t>26.0289682</t>
+  </si>
+  <si>
+    <t>26.0111758</t>
+  </si>
+  <si>
+    <t>26.0891867</t>
+  </si>
+  <si>
+    <t>26.0362972</t>
+  </si>
+  <si>
+    <t>26.1266001</t>
   </si>
   <si>
     <t>https://www.sasgym.ro/</t>
@@ -1048,24 +967,6 @@
     <t>https://www.phoenix-gym.ro/</t>
   </si>
   <si>
-    <t>https://befit.ro/cluburi-befit/oradea-magnolia</t>
-  </si>
-  <si>
-    <t>https://fit4u.ro/</t>
-  </si>
-  <si>
-    <t>https://www.oxygengym.ro/</t>
-  </si>
-  <si>
-    <t>https://arad.smartfitstudio.ro/</t>
-  </si>
-  <si>
-    <t>https://rockfitstudio.ro/</t>
-  </si>
-  <si>
-    <t>https://therockgym.ro/</t>
-  </si>
-  <si>
     <t>https://fitnessandspa.ro/</t>
   </si>
   <si>
@@ -1084,12 +985,6 @@
     <t>https://www.fitnessfloreasca.ro/</t>
   </si>
   <si>
-    <t>https://www.gladiatorfitness.ro/</t>
-  </si>
-  <si>
-    <t>https://www.athleticsportcenter.ro/</t>
-  </si>
-  <si>
     <t>https://freshclub.ro/public/programari-online/index.html</t>
   </si>
   <si>
@@ -1102,43 +997,91 @@
     <t>https://elite-gym.ro/</t>
   </si>
   <si>
-    <t>https://www.friendsarena.ro/</t>
-  </si>
-  <si>
-    <t>https://www.gymone.ro/</t>
-  </si>
-  <si>
-    <t>https://csextreme.ro/</t>
-  </si>
-  <si>
     <t>https://sweat.ro/the-light/</t>
   </si>
   <si>
     <t>https://sweat.ro/promenada/</t>
   </si>
   <si>
-    <t>https://www.studioc.ro/</t>
-  </si>
-  <si>
-    <t>https://areagym.ro/brasov/</t>
-  </si>
-  <si>
-    <t>https://18gym.ro/locatii-18gym-brasov/</t>
-  </si>
-  <si>
     <t>https://www.shape-up.ro/</t>
   </si>
   <si>
-    <t>+40770316651</t>
-  </si>
-  <si>
-    <t>+40738711661</t>
-  </si>
-  <si>
-    <t>+40765839511</t>
-  </si>
-  <si>
-    <t>+40756161500</t>
+    <t>https://shop.fitactive.ro/</t>
+  </si>
+  <si>
+    <t>https://www.anturajfitness.ro/</t>
+  </si>
+  <si>
+    <t>https://www.onyxclub.ro/orar-clase/</t>
+  </si>
+  <si>
+    <t>https://www.clubelite.ro/</t>
+  </si>
+  <si>
+    <t>https://www.absolutegym.ro/</t>
+  </si>
+  <si>
+    <t>https://downtownfitness.ro/vitan/</t>
+  </si>
+  <si>
+    <t>https://www.stayfit.ro/</t>
+  </si>
+  <si>
+    <t>https://www.worldclass.ro/club/worldclass-bucuresti-bucuresti-mall/</t>
+  </si>
+  <si>
+    <t>https://stayfit.ro/bucuresti/pipera/</t>
+  </si>
+  <si>
+    <t>https://www.clubunisports.ro/</t>
+  </si>
+  <si>
+    <t>https://fitness-academy.ro/</t>
+  </si>
+  <si>
+    <t>https://www.humanfitness.ro/</t>
+  </si>
+  <si>
+    <t>https://stayfit.ro/bucuresti/pantelimon/</t>
+  </si>
+  <si>
+    <t>https://ladyfit.ro/</t>
+  </si>
+  <si>
+    <t>https://www.fitclass.ro/</t>
+  </si>
+  <si>
+    <t>https://downtownfitness.ro/</t>
+  </si>
+  <si>
+    <t>https://downtownfitness.ro/descopera-matei-basarab/</t>
+  </si>
+  <si>
+    <t>https://www.downtownfitness.ro/</t>
+  </si>
+  <si>
+    <t>https://groovebox.ro/</t>
+  </si>
+  <si>
+    <t>https://www.uzina.ro/</t>
+  </si>
+  <si>
+    <t>https://www.unbrokenspirit.ro/</t>
+  </si>
+  <si>
+    <t>https://stayfit.ro/bucuresti/liberty/</t>
+  </si>
+  <si>
+    <t>https://www.bodyfitbucuresti.ro/contact/</t>
+  </si>
+  <si>
+    <t>https://www.royalfitnessclub.ro/</t>
+  </si>
+  <si>
+    <t>https://bestfitness.ro/</t>
+  </si>
+  <si>
+    <t>https://go700.ro/</t>
   </si>
   <si>
     <t>+40722847104</t>
@@ -1156,39 +1099,6 @@
     <t>+40770515842</t>
   </si>
   <si>
-    <t>+40751022826</t>
-  </si>
-  <si>
-    <t>+40359402552</t>
-  </si>
-  <si>
-    <t>+40732009923</t>
-  </si>
-  <si>
-    <t>+40770403715</t>
-  </si>
-  <si>
-    <t>+40770778899</t>
-  </si>
-  <si>
-    <t>+40770464762</t>
-  </si>
-  <si>
-    <t>+40758870470</t>
-  </si>
-  <si>
-    <t>+40771663575</t>
-  </si>
-  <si>
-    <t>+40775610556</t>
-  </si>
-  <si>
-    <t>+40722668307</t>
-  </si>
-  <si>
-    <t>+40773960342</t>
-  </si>
-  <si>
     <t>+40371111370</t>
   </si>
   <si>
@@ -1207,15 +1117,6 @@
     <t>+40735145548</t>
   </si>
   <si>
-    <t>+40732782000</t>
-  </si>
-  <si>
-    <t>+40753844997</t>
-  </si>
-  <si>
-    <t>+40741682665</t>
-  </si>
-  <si>
     <t>+40728115239</t>
   </si>
   <si>
@@ -1228,49 +1129,106 @@
     <t>+40723391502</t>
   </si>
   <si>
-    <t>+40256224645</t>
-  </si>
-  <si>
-    <t>+40799919610</t>
-  </si>
-  <si>
-    <t>+40755115990</t>
-  </si>
-  <si>
-    <t>+40731749656</t>
-  </si>
-  <si>
-    <t>+40740862273</t>
-  </si>
-  <si>
-    <t>+40727898822</t>
-  </si>
-  <si>
     <t>+40770642390</t>
   </si>
   <si>
     <t>+40770638220</t>
   </si>
   <si>
-    <t>+40371188364</t>
-  </si>
-  <si>
-    <t>+40742473033</t>
-  </si>
-  <si>
-    <t>+40732744453</t>
-  </si>
-  <si>
-    <t>+40748906070</t>
-  </si>
-  <si>
     <t>+40731122100</t>
   </si>
   <si>
-    <t>office@fitnesshunedoara.ro</t>
-  </si>
-  <si>
-    <t>office@grand-fitness.ro</t>
+    <t>+40758987111</t>
+  </si>
+  <si>
+    <t>+40741138330</t>
+  </si>
+  <si>
+    <t>+40761337320</t>
+  </si>
+  <si>
+    <t>+40749259259</t>
+  </si>
+  <si>
+    <t>+40733770066</t>
+  </si>
+  <si>
+    <t>+40767960775</t>
+  </si>
+  <si>
+    <t>+40770411222</t>
+  </si>
+  <si>
+    <t>+40783041116</t>
+  </si>
+  <si>
+    <t>+40749248816</t>
+  </si>
+  <si>
+    <t>+40770969792</t>
+  </si>
+  <si>
+    <t>+40733688434</t>
+  </si>
+  <si>
+    <t>+40728816263</t>
+  </si>
+  <si>
+    <t>+40771600700</t>
+  </si>
+  <si>
+    <t>+40770860181</t>
+  </si>
+  <si>
+    <t>+40726438348</t>
+  </si>
+  <si>
+    <t>+40760600101</t>
+  </si>
+  <si>
+    <t>+40733412100</t>
+  </si>
+  <si>
+    <t>+40748140401</t>
+  </si>
+  <si>
+    <t>+40314380829</t>
+  </si>
+  <si>
+    <t>+40213300787</t>
+  </si>
+  <si>
+    <t>+40750435289</t>
+  </si>
+  <si>
+    <t>+40727226255</t>
+  </si>
+  <si>
+    <t>+40740269769</t>
+  </si>
+  <si>
+    <t>+40771268071</t>
+  </si>
+  <si>
+    <t>+40770240612</t>
+  </si>
+  <si>
+    <t>+40767186768</t>
+  </si>
+  <si>
+    <t>+40755016043</t>
+  </si>
+  <si>
+    <t>+40727833685</t>
+  </si>
+  <si>
+    <t>+40215700700</t>
+  </si>
+  <si>
+    <t>+40722205581</t>
+  </si>
+  <si>
+    <t>+40758838605</t>
   </si>
   <si>
     <t>server@www.sasgym.ro</t>
@@ -1285,27 +1243,9 @@
     <t>contact@phoenix-gym.ro</t>
   </si>
   <si>
-    <t>contact@befit.ro</t>
-  </si>
-  <si>
-    <t>contact@fit4u.ro</t>
-  </si>
-  <si>
-    <t>contact@oxygengym.ro</t>
-  </si>
-  <si>
-    <t>office@smartfitstudio.ro</t>
-  </si>
-  <si>
-    <t>contact@therockgym.ro</t>
-  </si>
-  <si>
     <t>bogdannionut@yahoo.com</t>
   </si>
   <si>
-    <t>contact@gladiatorfitness.ro</t>
-  </si>
-  <si>
     <t>contact@freshclub.ro</t>
   </si>
   <si>
@@ -1315,37 +1255,46 @@
     <t>contact@ifit-ifun.com</t>
   </si>
   <si>
-    <t>office@friendsarena.ro</t>
-  </si>
-  <si>
-    <t>contact@gymone.ro</t>
-  </si>
-  <si>
-    <t>office@csextreme.ro</t>
-  </si>
-  <si>
     <t>contact@sweat.ro</t>
   </si>
   <si>
-    <t>office@www.studioc.ro</t>
-  </si>
-  <si>
-    <t>contact@areagym.ro</t>
-  </si>
-  <si>
     <t>contact@shape-up.ro</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/place/Fitness+4+All+Hunedoara/data=!4m7!3m6!1s0x474e8a5883569dd9:0x4005109328c46127!8m2!3d45.7593955!4d22.9081019!16s%2Fg%2F11ggr7gn3y!19sChIJ2Z1Wg1iKTkcRJ2HEKJMQBUA?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Elite+Center+Hunedoara/data=!4m7!3m6!1s0x474e8b0012882ef9:0x5dc884f8520ca4a0!8m2!3d45.7512288!4d22.9048309!16s%2Fg%2F11y3wx47g_!19sChIJ-S6IEgCLTkcRoKQMUviEyF0?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Fitness+World+Studio/data=!4m7!3m6!1s0x474e8b38af66829b:0x55a9d31e41900abf!8m2!3d45.7538679!4d22.9100183!16s%2Fg%2F11y3lx4302!19sChIJm4JmrziLTkcRvwqQQR7TqVU?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Grand+Fitness/@45.6796782,25.6147359,17z/data=!3m1!4b1!4m6!3m5!1s0x40b35be4072313f1:0x302ca3e4b9e1889d!8m2!3d45.6796782!4d25.6147359!16s%2Fg%2F12lk6197n?hl=ro&amp;entry=ttu&amp;g_ep=EgoyMDI2MDQxNS4wIKXMDSoASAFQAw%3D%3D</t>
+    <t>vitan@fitactive.ro</t>
+  </si>
+  <si>
+    <t>contact@anturajfitness.ro</t>
+  </si>
+  <si>
+    <t>hello@downtownfitness.ro</t>
+  </si>
+  <si>
+    <t>receptie.pipera@stayfit.ro</t>
+  </si>
+  <si>
+    <t>office@fitness-academy.ro</t>
+  </si>
+  <si>
+    <t>contact@humanfitness.ro</t>
+  </si>
+  <si>
+    <t>contact@ladyfit.ro</t>
+  </si>
+  <si>
+    <t>office@groovebox.ro</t>
+  </si>
+  <si>
+    <t>contact@uzina.ro</t>
+  </si>
+  <si>
+    <t>receptie.liberty@stayfit.ro</t>
+  </si>
+  <si>
+    <t>salonbodyfit@gmail.com</t>
+  </si>
+  <si>
+    <t>royalfitnessclub@gmail.com</t>
   </si>
   <si>
     <t>https://www.google.com/maps/place/Sas+Gym/data=!4m7!3m6!1s0x40b1fedd08f15d0f:0x79c7050ec01cf4d1!8m2!3d44.4222366!4d26.1335111!16s%2Fg%2F12lk2ggbq!19sChIJD13xCN3-sUAR0fQcwA4Fx3k?authuser=0&amp;hl=ro&amp;rclk=1</t>
@@ -1363,42 +1312,6 @@
     <t>https://www.google.com/maps/place/Phoenix+Gym/data=!4m7!3m6!1s0x40b1f961cd046d1d:0x8961b1a38fe655c3!8m2!3d44.4451266!4d26.1109722!16s%2Fg%2F11h8tvr6r3!19sChIJHW0EzWH5sUARw1Xmj6OxYYk?authuser=0&amp;hl=ro&amp;rclk=1</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/place/BEFIT+Magnolia/data=!4m7!3m6!1s0x474649ef02a65be7:0xd8631ea31cb3f73c!8m2!3d47.0777171!4d21.916341!16s%2Fg%2F11ypwgz8bm!19sChIJ51umAu9JRkcRPPezHKMeY9g?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Get+Fit/data=!4m7!3m6!1s0x4746395d0be8e6cf:0x4279bb6a5c09d6de!8m2!3d47.0369936!4d21.948661!16s%2Fg%2F11h1ssptlk!19sChIJz-boC105RkcR3tYJXGq7eUI?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/FIT4U+Primariei/data=!4m7!3m6!1s0x474647dcc67de1a1:0xaf68e0f9a1d55162!8m2!3d47.0569!4d21.9220657!16s%2Fg%2F11ckqn6kfr!19sChIJoeF9xtxHRkcRYlHVofngaK8?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Oxygen+Gym+Nufaru/data=!4m7!3m6!1s0x474639721c8bdc8f:0x9cce19b8c9ac34a1!8m2!3d47.0284461!4d21.9606208!16s%2Fg%2F11lq281fx5!19sChIJj9yLHHI5RkcRoTSsybgZzpw?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Dynamic+Oradea/data=!4m7!3m6!1s0x474647eb9c37fc75:0x3301e09b77549e7c!8m2!3d47.0475755!4d21.9262121!16s%2Fg%2F11gbk4xpm4!19sChIJdfw3nOtHRkcRfJ5Ud5vgATM?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/SmartFit+Studio+Arad/data=!4m7!3m6!1s0x4745991c57fa2eed:0x5c8164b4dc51185b!8m2!3d46.1796527!4d21.3220356!16s%2Fg%2F11nmc73yrc!19sChIJ7S76VxyZRUcRWxhR3LRkgVw?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/CLASSIC+GYM+ARAD/data=!4m7!3m6!1s0x474598fff6178d0f:0xd029d9b8f54ca23c!8m2!3d46.1752618!4d21.3176014!16s%2Fg%2F11c1w0rsjt!19sChIJD40X9v-YRUcRPKJM9bjZKdA?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Rock+Fit+Studio+Arad/data=!4m7!3m6!1s0x474599f1387d8503:0xc35be6f2369ed704!8m2!3d46.1884859!4d21.3289526!16s%2Fg%2F11vd8cjgg5!19sChIJA4V9OPGZRUcRBNeeNvLmW8M?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Stay+Fit+Gym+Afi+Arad/data=!4m7!3m6!1s0x4745994118b3251b:0x916661684cfd9a8a!8m2!3d46.1905816!4d21.3187622!16s%2Fg%2F11w4q97fk3!19sChIJGyWzGEGZRUcRipr9TGhhZpE?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Stay+Fit+Gym+Vladimirescu+Arad/data=!4m7!3m6!1s0x47459bec200b596b:0x75c2131c1b6df5db!8m2!3d46.1669616!4d21.3876604!16s%2Fg%2F11x0q7nd0c!19sChIJa1kLIOybRUcR2_VtGxwTwnU?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Tim+Gym/data=!4m7!3m6!1s0x40b32997c5407b9f:0x8fb038bf38149e50!8m2!3d45.2696367!4d25.0432155!16s%2Fg%2F11h7rhqcpc!19sChIJn3tAxZcps0ARUJ4UOL84sI8?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/The+Rock+Gym/@47.1590905,27.5969389,17z/data=!3m1!4b1!4m6!3m5!1s0x40cafbe87ae106cf:0x8a24a1b9f847991d!8m2!3d47.1590905!4d27.5969389!16s%2Fg%2F11shv0m9s1?hl=ro&amp;entry=ttu&amp;g_ep=EgoyMDI2MDQxNS4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps/place/Alexandreea+Club+Fitness+%26+Spa+%7C+Piscin%C4%83,+Fitness,+Aerobic,Teren+Fotbal,+Spinning+%7C+Initiere+Inot+Copii+%26+Adulti/data=!4m7!3m6!1s0x40b1fecde3663d13:0x8ba512346a10b13d!8m2!3d44.433388!4d26.1493624!16s%2Fg%2F1v8y2jy8!19sChIJEz1m483-sUARPbEQajQSpYs?authuser=0&amp;hl=ro&amp;rclk=1</t>
   </si>
   <si>
@@ -1420,15 +1333,6 @@
     <t>https://www.google.com/maps/place/Sala+Fitness+Floreasca+GYM+-+Dorobanti/data=!4m7!3m6!1s0x40b1f8a41c499255:0x293e4c5b52288278!8m2!3d44.4621476!4d26.1059935!16s%2Fg%2F11c58svyvl!19sChIJVZJJHKT4sUAReIIoUltMPik?authuser=0&amp;hl=ro&amp;rclk=1</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/place/Saba+Gym/data=!4m7!3m6!1s0x40b21cba953c6257:0x7e31595dc5b4b7bb!8m2!3d44.5462088!4d26.072956!16s%2Fg%2F1q62dzls5!19sChIJV2I8lbocskARu7e0xV1ZMX4?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Sal%C4%83+de+fitness+Gladiator/@47.9276157,23.8991475,17z/data=!3m1!4b1!4m6!3m5!1s0x4737bbaf2ab233f9:0x6deb4e3b26811acb!8m2!3d47.9276157!4d23.8991475!16s%2Fg%2F11bwprthwg?hl=ro&amp;entry=ttu&amp;g_ep=EgoyMDI2MDQxNS4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Athletic+Sport+Center/data=!4m7!3m6!1s0x47490db843a47d29:0x85fe5176fc403b23!8m2!3d46.7604077!4d23.6134888!16s%2Fg%2F11kjpps8gg!19sChIJKX2kQ7gNSUcRIztA_HZR_oU?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps/place/Fresh+Club+-+Sala+Aerobic+si+Fitness+Bucuresti/data=!4m7!3m6!1s0x40b1fee315a2d1c9:0x47903ec803e5918f!8m2!3d44.4163447!4d26.1207801!16s%2Fg%2F1tfb0hh0!19sChIJydGiFeP-sUARj5HlA8g-kEc?authuser=0&amp;hl=ro&amp;rclk=1</t>
   </si>
   <si>
@@ -1441,63 +1345,111 @@
     <t>https://www.google.com/maps/place/Elite+Gym/data=!4m7!3m6!1s0x40b1ff2c795486c9:0x11287a6422d3a90a!8m2!3d44.4246115!4d26.1241463!16s%2Fg%2F11fcq_z8g9!19sChIJyYZUeSz_sUARCqnTImR6KBE?authuser=0&amp;hl=ro&amp;rclk=1</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/place/Friend%27s+Arena+S.R.L./data=!4m7!3m6!1s0x47455d0f5c5c8a57:0x931ce6dfc1f909b2!8m2!3d45.7348408!4d21.1979777!16s%2Fg%2F1hc2n47l2!19sChIJV4pcXA9dRUcRsgn5wd_mHJM?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Gym+One+2/data=!4m7!3m6!1s0x47455d0067f1fd8f:0x91d9e16a4c6c989a!8m2!3d45.728441!4d21.2333851!16s%2Fg%2F11y01y32t6!19sChIJj_3xZwBdRUcRmphsTGrh2ZE?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Gym+One+5/data=!4m7!3m6!1s0x474567c4a8f0488d:0xfffdddad4193916b!8m2!3d45.757149!4d21.2180043!16s%2Fg%2F11fshn9h4h!19sChIJjUjwqMRnRUcRa5GTQa3d_f8?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Fit4Life+Gym/data=!4m7!3m6!1s0x474567fcaa599df9:0x11349d586267ee77!8m2!3d45.772103!4d21.21652!16s%2Fg%2F11q8sjxndz!19sChIJ-Z1ZqvxnRUcRd-5nYlidNBE?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Haltere+Club+Timi%C8%99oara/data=!4m7!3m6!1s0x47456788ab4a2bd7:0x8af07ae1b672375f!8m2!3d45.7618612!4d21.2184097!16s%2Fg%2F11df8137j7!19sChIJ1ytKq4hnRUcRXzdytuF68Io?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/MY+GYM/@44.4031801,25.9540021,17z/data=!3m1!4b1!4m6!3m5!1s0x40adffa7be8e83cf:0xc10f2b6c97188ae0!8m2!3d44.4031801!4d25.9540021!16s%2Fg%2F11ssfqwz_m?hl=ro&amp;entry=ttu&amp;g_ep=EgoyMDI2MDQxNS4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Extreme/data=!4m7!3m6!1s0x40b1fea17e375841:0x6b39b0673ad64370!8m2!3d44.415376!4d26.1692759!16s%2Fg%2F1td68cgr!19sChIJQVg3fqH-sUARcEPWOmewOWs?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps/place/Sweat+-+The+Light/data=!4m7!3m6!1s0x40b2011c97f84f45:0x5e734955c81e125a!8m2!3d44.4347598!4d26.0506442!16s%2Fg%2F11kfpyfkyl!19sChIJRU_4lxwBskARWhIeyFVJc14?authuser=0&amp;hl=ro&amp;rclk=1</t>
   </si>
   <si>
     <t>https://www.google.com/maps/place/Sweat+-+Promenada+-+Zone+313/data=!4m7!3m6!1s0x40b20358076851dd:0x5e2d0306d109adda!8m2!3d44.4766311!4d26.106114!16s%2Fg%2F11fthj48sn!19sChIJ3VFoB1gDskAR2q0J0QYDLV4?authuser=0&amp;hl=ro&amp;rclk=1</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/place/Studio+C/data=!4m7!3m6!1s0x40b35b8013f3b7cd:0x5f5b9312424b7464!8m2!3d45.6478786!4d25.606302!16s%2Fg%2F1hhl841sn!19sChIJzbfzE4Bbs0ARZHRLQhKTW18?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Area+Gym+-+Brasov+-+Unirea/data=!4m7!3m6!1s0x40b35ba2507fe445:0x45703af0003d451d!8m2!3d45.6611188!4d25.6105991!16s%2Fg%2F11w8tmkg9d!19sChIJReR_UKJbs0ARHUU9APA6cEU?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/18GYM+Unirea+Mall+Brasov/data=!4m7!3m6!1s0x40b35b0b09376007:0xd911eda7eb1b699e!8m2!3d45.6611188!4d25.6105991!16s%2Fg%2F11t_swj3vq!19sChIJB2A3CQtbs0ARnmkb66ftEdk?authuser=0&amp;hl=ro&amp;rclk=1</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Abc/@47.5697137,26.2749884,17z/data=!3m1!4b1!4m6!3m5!1s0x4734fc367793a771:0xef7111dd2c8362a!8m2!3d47.5697137!4d26.2749884!16s%2Fg%2F11cs2h7t5m?hl=ro&amp;entry=ttu&amp;g_ep=EgoyMDI2MDQxNS4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/place/Fitfinity+Gym+Endorfine/@47.0221332,21.9238989,17z/data=!3m1!4b1!4m6!3m5!1s0x47464778d45c2079:0x4830b8e9c1b62eb0!8m2!3d47.0221332!4d21.9238989!16s%2Fg%2F11y2fc32g4?hl=ro&amp;entry=ttu&amp;g_ep=EgoyMDI2MDQxNS4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
     <t>https://www.google.com/maps/place/SHAPE+UP+STUDIO+UNIRII/data=!4m7!3m6!1s0x40b1ff3d82c46ec9:0x51ee99160b6c361c!8m2!3d44.428577!4d26.1076559!16s%2Fg%2F11bymsnmd9!19sChIJyW7Egj3_sUARHDZsCxaZ7lE?authuser=0&amp;hl=ro&amp;rclk=1</t>
   </si>
   <si>
-    <t>luni: 08-22; marți: 08-22; miercuri: 08-22; joi: 08-22; vineri: 08-22; sâmbătă: 09-22; duminică: 10-20</t>
-  </si>
-  <si>
-    <t>luni: 18-19:30; marți: Închis; miercuri: 18-19:30; joi: 18-19:30; vineri: Închis; sâmbătă: Închis; duminică: Închis</t>
+    <t>https://www.google.com/maps/place/FITACTIVE+Bucure%C8%99ti+Vitan/data=!4m7!3m6!1s0x40b1ff9eef1436f7:0xd22a1933c5407872!8m2!3d44.4057611!4d26.1424972!16s%2Fg%2F11vy14t96m!19sChIJ9zYU757_sUARcnhAxTMZKtI?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gym+Life/data=!4m7!3m6!1s0x40b1fdf669a69259:0x2a63f04712c23864!8m2!3d44.4197561!4d26.1998143!16s%2Fg%2F11mdp66gtw!19sChIJWZKmafb9sUARZDjCEkfwYyo?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Anturaj+Fitness/data=!4m7!3m6!1s0x40b1ffd0b551055d:0x3f4c44611c6b8639!8m2!3d44.3978336!4d26.1114818!16s%2Fg%2F11h3z8bh5w!19sChIJXQVRtdD_sUAROYZrHGFETD8?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Onyx+Fitness+Club+-+Sala+Fitness+Aerobic/data=!4m7!3m6!1s0x40ae01fdf19fe42f:0xfce074c89706b6c0!8m2!3d44.338842!4d26.094125!16s%2Fg%2F11h_c7syv_!19sChIJL-Sf8f0BrkARwLYGl8h04Pw?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Club+Elite/data=!4m7!3m6!1s0x40b1f9cf3c5991d1:0x241d9d79cd9677a6!8m2!3d44.4901857!4d26.2006478!16s%2Fg%2F1td0d_m9!19sChIJ0ZFZPM_5sUARpneWzXmdHSQ?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Absolute+Gym/@44.4109937,26.0551191,17z/data=!3m1!4b1!4m6!3m5!1s0x40b1ff1cc2ed666f:0x6c189d61b5f61f49!8m2!3d44.4109937!4d26.0551191!16s%2Fg%2F11tdcp84nn?hl=ro&amp;entry=ttu&amp;g_ep=EgoyMDI2MDQxNS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Downtown+Fitness+Vitan/data=!4m7!3m6!1s0x40b1ff5123c5041d:0xebd84197ffee1476!8m2!3d44.4230563!4d26.1243049!16s%2Fg%2F11x8qrw1ck!19sChIJHQTFI1H_sUARdhTu_5dB2Os?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Stay+Fit/data=!4m7!3m6!1s0x40b1ff2b5514d3cf:0x2e9984d49d754e3c!8m2!3d44.413194!4d26.1382356!16s%2Fg%2F11h2c3nd1c!19sChIJz9MUVSv_sUARPE51ndSEmS4?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/World+Class+Bucure%C8%99ti+Bucure%C8%99ti+Mall/data=!4m7!3m6!1s0x40b1ffc9148e7df9:0xa073fe29f2de1403!8m2!3d44.4210354!4d26.1272093!16s%2Fg%2F11gh9nywd2!19sChIJ-X2OFMn_sUARAxTe8in-c6A?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Stay+Fit+Gym+-+Pipera/@44.4846143,26.1196758,17z/data=!3m1!4b1!4m6!3m5!1s0x40b1f92ef1306a53:0xcd55f01c7fcd09fc!8m2!3d44.4846143!4d26.1196758!16s%2Fg%2F11fwxbzb_f?hl=ro&amp;entry=ttu&amp;g_ep=EgoyMDI2MDQxOS4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Uni+Sports+Cotroceni/data=!4m7!3m6!1s0x40b1ff7e7f7edbb9:0x638256d3150fab76!8m2!3d44.424293!4d26.064029!16s%2Fg%2F11c523pnds!19sChIJudt-f37_sUARdqsPFdNWgmM?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fitness+Academy+Rahova/data=!4m7!3m6!1s0x40b1ff92cc092145:0x3d1ff0692aa96663!8m2!3d44.4169382!4d26.0811803!16s%2Fg%2F11gyxcrjpk!19sChIJRSEJzJL_sUARY2apKmnwHz0?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Human+Fitness/data=!4m7!3m6!1s0x40b1ffee96bef67f:0x91037863c0df0641!8m2!3d44.4263083!4d26.1237868!16s%2Fg%2F11g4h2zlyj!19sChIJf_a-lu7_sUARQQbfwGN4A5E?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Stay+Fit+Gym/data=!4m7!3m6!1s0x40b1f92ff495235d:0xa67b9131c2d3d501!8m2!3d44.445146!4d26.1575!16s%2Fg%2F11b86x_xj4!19sChIJXSOV9C_5sUARAdXTwjGRe6Y?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/LadyFIT/data=!4m7!3m6!1s0x40b1ff3e719d1e93:0xfb3c89c49f3b4a21!8m2!3d44.4303977!4d26.1049864!16s%2Fg%2F11b7lfdl6n!19sChIJkx6dcT7_sUARIUo7n8SJPPs?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/FitClass+Club/data=!4m7!3m6!1s0x40b1febd5284f735:0x44fea0fdda41069c!8m2!3d44.415647!4d26.160987!16s%2Fg%2F12hrmwt7t!19sChIJNfeEUr3-sUARnAZB2v2g_kQ?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Downtown+Fitness+Obor/data=!4m7!3m6!1s0x40b1f94eb8359db7:0x4f86835ddbb22462!8m2!3d44.4502806!4d26.1276169!16s%2Fg%2F11j1hx2kr1!19sChIJt501uE75sUARYiSy212Dhk8?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Downtown+Fitness+%26+SPA+Matei+Basarab/data=!4m7!3m6!1s0x40b1ff59011a900d:0x7e640df2bd49d36a!8m2!3d44.4313552!4d26.1287753!16s%2Fg%2F11vrkkzpst!19sChIJDZAaAVn_sUARatNJvfINZH4?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Downtown+Fitness+Mihalache/data=!4m7!3m6!1s0x40b2021cc6f2bc7b:0xdb4a15d8e2189eee!8m2!3d44.4586368!4d26.0774563!16s%2Fg%2F11b76h7bh3!19sChIJe7zyxhwCskAR7p4Y4tgVSts?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Enjoy+Fitness+club+%28fost+Animal+Kingdom%29/data=!4m7!3m6!1s0x40b1ff1a4e6c92e3:0x14d1cad1b59b4661!8m2!3d44.4212284!4d26.1072313!16s%2Fg%2F11r8hqqky!19sChIJ45JsThr_sUARYUabtdHK0RQ?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Groove+BOX/data=!4m7!3m6!1s0x40b1ff74f4bffaab:0x2d8d0bb3449ba97a!8m2!3d44.4193026!4d26.0809958!16s%2Fg%2F11bbt5v5sk!19sChIJq_q_9HT_sUAReqmbRLMLjS0?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Uzina/data=!4m7!3m6!1s0x40b1fedaebc59fcb:0x23a33f7847fc6058!8m2!3d44.4116403!4d26.1180163!16s%2Fg%2F12mkw8x2k!19sChIJy5_F69r-sUARWGD8R3g_oyM?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/CrossFit+Unbroken+Spirit/data=!4m7!3m6!1s0x40b1ff2ad7df5f99:0x83693788dcfc4734!8m2!3d44.408234!4d26.126472!16s%2Fg%2F11zksnl5sh!19sChIJmV_f1yr_sUARNEf83Ig3aYM?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Stay+Fit+Gym+Liberty/data=!4m7!3m6!1s0x40b1ff9fd865b385:0xba081a0f031dfb01!8m2!3d44.414964!4d26.0806565!16s%2Fg%2F11by_dtxhw!19sChIJhbNl2J__sUARAfsdAw8aCLo?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jungle+Gym+Bucuresti/data=!4m7!3m6!1s0x40b1ff4d2bd98ea9:0x7a7f63be1ca34600!8m2!3d44.3842981!4d26.1017181!16s%2Fg%2F11ltq4s1r7!19sChIJqY7ZK03_sUARAEajHL5jf3o?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/BODYFIT/data=!4m7!3m6!1s0x40b1f8a5c6975d49:0xab8449a7d1b92712!8m2!3d44.4600394!4d26.1049808!16s%2Fg%2F11bbrnk85z!19sChIJSV2XxqX4sUAREie50adJhKs?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Royal+Fitness+Club/data=!4m7!3m6!1s0x40b201b100a3f06f:0x9e563794eb44f1e4!8m2!3d44.4344494!4d26.0289682!16s%2Fg%2F11cfghdvg!19sChIJb_CjALEBskAR5PFE65Q3Vp4?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Best+Fitness+Gym/data=!4m7!3m6!1s0x40b200505aa97c33:0x148bbb22c4a467e0!8m2!3d44.4238835!4d26.0111758!16s%2Fg%2F11b7cgdrqb!19sChIJM3ypWlAAskAR4GekxCK7ixQ?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/700+Fit+Club/data=!4m7!3m6!1s0x40b2025f3d25b4cd:0x81064a6aa968050b!8m2!3d44.4902411!4d26.0891867!16s%2Fg%2F11fyzf6tzr!19sChIJzbQlPV8CskARCwVoqWpKBoE?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/700+Fit+Club+-+Drumul+Taberei/data=!4m7!3m6!1s0x40b201d12607c3ef:0xdeac4ae6e3fd8038!8m2!3d44.4170484!4d26.0362972!16s%2Fg%2F11frdsdnk3!19sChIJ78MHJtEBskAROID94-ZKrN4?authuser=0&amp;hl=ro&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/New+Fit+Way/data=!4m7!3m6!1s0x40b1ff838ce4fb6f:0x874208dec7d27c02!8m2!3d44.4556808!4d26.1266001!16s%2Fg%2F11cn5s_pm4!19sChIJb_vkjIP_sUARAnzSx94IQoc?authuser=0&amp;hl=ro&amp;rclk=1</t>
   </si>
   <si>
     <t>luni: Deschis 24 de ore; marți: Deschis 24 de ore; miercuri: Deschis 24 de ore; joi: Deschis 24 de ore; vineri: Deschis 24 de ore; sâmbătă: Deschis 24 de ore; duminică: Deschis 24 de ore</t>
   </si>
   <si>
-    <t>luni: 06-21:30; marți: 06-21:30; miercuri: 06-21:30; joi: 06-21:30; vineri: 06-21:30; sâmbătă: 08-14:30; duminică: 08:30-14:30</t>
-  </si>
-  <si>
     <t>luni: 07-22; marți: 07-22; miercuri: 07-22; joi: 07-22; vineri: 07-22; sâmbătă: 09-19; duminică: 09-19</t>
   </si>
   <si>
@@ -1510,36 +1462,6 @@
     <t>luni: 07-21:30; marți: 07-21:30; miercuri: 07-21:30; joi: 07-21:30; vineri: 07-21:30; sâmbătă: 09-18; duminică: 09-14</t>
   </si>
   <si>
-    <t>luni: 06-23; marți: 06-23; miercuri: 06-23; joi: 06-23; vineri: 06-23; sâmbătă: 06-23; duminică: 06-23</t>
-  </si>
-  <si>
-    <t>luni: 07-22; marți: 07-22; miercuri: 07-22; joi: 07-22; vineri: 07-22; sâmbătă: 08:30-19:30; duminică: Închis</t>
-  </si>
-  <si>
-    <t>luni: 06-00; marți: 06-00; miercuri: 06-00; joi: 06-00; vineri: 06-00; sâmbătă: 08-22; duminică: 10-20</t>
-  </si>
-  <si>
-    <t>luni: 07-13; marți: 07-13; miercuri: 07-13; joi: 07-13; vineri: 07-13; sâmbătă: Închis; duminică: Închis</t>
-  </si>
-  <si>
-    <t>luni: 07-22; marți: 07-22; miercuri: 07-22; joi: 07-22; vineri: 07-22; sâmbătă: 07-20; duminică: 10-16</t>
-  </si>
-  <si>
-    <t>luni: 10-22; marți: 10-22; miercuri: 10-22; joi: 10-22; vineri: 10-22; sâmbătă: 10-20; duminică: Închis</t>
-  </si>
-  <si>
-    <t>luni: 07-20; marți: 07-20; miercuri: 07-20; joi: 07-20; vineri: 07-20; sâmbătă: Închis; duminică: Închis</t>
-  </si>
-  <si>
-    <t>luni: 07-23; marți: 07-23; miercuri: 07-23; joi: 07-23; vineri: 07-23; sâmbătă: 10-22; duminică: 10-22</t>
-  </si>
-  <si>
-    <t>luni: 08-12; marți: 08-12; miercuri: 08-12; joi: 08-12; vineri: 08-12; sâmbătă: Închis; duminică: Închis</t>
-  </si>
-  <si>
-    <t>luni: 06-00; marți: 06-00; miercuri: 06-00; joi: 06-00; vineri: 06-00; sâmbătă: 06-00; duminică: 06-00</t>
-  </si>
-  <si>
     <t>luni: 07:30-22; marți: 07:30-22; miercuri: 07:30-22; joi: 07:30-22; vineri: 07:30-22; sâmbătă: 08-17; duminică: 08-15</t>
   </si>
   <si>
@@ -1555,12 +1477,6 @@
     <t>luni: 06-22; marți: 06-22; miercuri: 06-22; joi: 06-22; vineri: 06-22; sâmbătă: 09-18; duminică: 09-14</t>
   </si>
   <si>
-    <t>luni: 08-22; marți: 08-22; miercuri: 08-22; joi: 08-22; vineri: 08-22; sâmbătă: 09-17; duminică: 09-17</t>
-  </si>
-  <si>
-    <t>luni: 07-22; marți: 07-22; miercuri: 07-22; joi: 07-22; vineri: 07-22; sâmbătă: 09-20; duminică: 09-18</t>
-  </si>
-  <si>
     <t>luni: 08-21; marți: 08-21; miercuri: 08-21; joi: 08-21; vineri: 08-21; sâmbătă: 08-14; duminică: Închis</t>
   </si>
   <si>
@@ -1573,49 +1489,97 @@
     <t>luni: 07-22; marți: 07-22; miercuri: 07-22; joi: 07-22; vineri: 07-22; sâmbătă: 09-17; duminică: 09-17</t>
   </si>
   <si>
-    <t>luni: 07-23; marți: 07-23; miercuri: 07-23; joi: 07-23; vineri: 07-23; sâmbătă: 08:30-22; duminică: 08:30-14</t>
-  </si>
-  <si>
-    <t>luni: 06-00; marți: 06-00; miercuri: 06-00; joi: 06-00; vineri: 06-00; sâmbătă: 09-00; duminică: 09-00</t>
-  </si>
-  <si>
-    <t>luni: 07:30-22:30; marți: 07:30-22:30; miercuri: 07:30-22:30; joi: 07:30-22:30; vineri: 07:30-22:30; sâmbătă: 10-13; duminică: 18-20</t>
-  </si>
-  <si>
-    <t>luni: 06-23; marți: 06-23; miercuri: 06-23; joi: 06-23; vineri: 06-23; sâmbătă: 09-21; duminică: 09-21</t>
-  </si>
-  <si>
-    <t>luni: 09-00; marți: 09-00; miercuri: 09-00; joi: 09-00; vineri: 09-00; sâmbătă: 09-18; duminică: 09-18</t>
-  </si>
-  <si>
     <t>luni: 06-22; marți: 06-22; miercuri: 06-22; joi: 06-22; vineri: 06-22; sâmbătă: 09-19; duminică: 09-19</t>
   </si>
   <si>
-    <t>luni: 08-22; marți: 08-22; miercuri: 08-22; joi: 08-22; vineri: 08-22; sâmbătă: 09-12; duminică: Închis</t>
-  </si>
-  <si>
-    <t>luni: 06-22; marți: 06-22; miercuri: 06-22; joi: 06-22; vineri: 06-22; sâmbătă: 10-20; duminică: 10-20</t>
-  </si>
-  <si>
-    <t>luni: 06-22; marți: 06-22; miercuri: 06-22; joi: 06-22; vineri: 06-22; sâmbătă: 08-15; duminică: 10-13</t>
-  </si>
-  <si>
     <t>luni: 08-20; marți: 08-20; miercuri: 08-20; joi: 08-20; vineri: 08-20; sâmbătă: 10-15; duminică: Închis</t>
   </si>
   <si>
+    <t>luni: 07-22; marți: 07-22; miercuri: 07-22; joi: 07-22; vineri: 07-22; sâmbătă: 08-16; duminică: 08-14</t>
+  </si>
+  <si>
+    <t>luni: 07-22; marți: 07-22; miercuri: 07-22; joi: 07-22; vineri: 07-22; sâmbătă: 09-18; duminică: 10-16</t>
+  </si>
+  <si>
+    <t>luni: 07-22; marți: 07-22; miercuri: 07-22; joi: 07-22; vineri: 07-22; sâmbătă: 09-16; duminică: 09-16</t>
+  </si>
+  <si>
+    <t>luni: 08-22:30; marți: 08-22; miercuri: 01-22; joi: 08-22; vineri: 01-22; sâmbătă: Închis; duminică: Închis</t>
+  </si>
+  <si>
+    <t>luni: 06-01; marți: 06-01; miercuri: 06-01; joi: 06-01; vineri: 06-01; sâmbătă: 08-20; duminică: 08-20</t>
+  </si>
+  <si>
+    <t>luni: 07-22; marți: 07-22; miercuri: 07-22; joi: 07-22; vineri: 07-22; sâmbătă: 08-22; duminică: 08-22</t>
+  </si>
+  <si>
+    <t>luni: 07-23; marți: 07-23; miercuri: 07-23; joi: 07-23; vineri: 07-23; sâmbătă: 09-18; duminică: 09-18</t>
+  </si>
+  <si>
+    <t>luni: 07-22; marți: 07-22; miercuri: 07-22; joi: 07-22; vineri: 07-22; sâmbătă: 08-18; duminică: 09-16</t>
+  </si>
+  <si>
+    <t>luni: 07-22; marți: 07-22; miercuri: 07-22; joi: 07-22; vineri: 07-22; sâmbătă: 07-14; duminică: Închis</t>
+  </si>
+  <si>
+    <t>luni: 07-22:30; marți: 07-22:30; miercuri: 07-22:30; joi: 07-22:30; vineri: 07-22:30; sâmbătă: 09-18; duminică: 09-18</t>
+  </si>
+  <si>
+    <t>luni: 06-22:30; marți: 06-22:30; miercuri: 06-22:30; joi: 06-22:30; vineri: 06-22:30; sâmbătă: 08-20; duminică: 08-20</t>
+  </si>
+  <si>
+    <t>luni: 06-22:30; marți: 06-22:30; miercuri: 06-22:30; joi: 06-22:30; vineri: 06-22:30; sâmbătă: 08-18; duminică: 08-18</t>
+  </si>
+  <si>
+    <t>luni: 07-22; marți: 07-22; miercuri: 07-22; joi: 07-22; vineri: 07-22; sâmbătă: 08-17; duminică: 08-17</t>
+  </si>
+  <si>
+    <t>luni: 08:30-21; marți: 12-21; miercuri: 08:30-21; joi: 12-21; vineri: 08:30-21; sâmbătă: 10-13:30; duminică: Închis</t>
+  </si>
+  <si>
+    <t>luni: 07-09; marți: 07-09; miercuri: 07-09; joi: 07-09; vineri: 07-09; sâmbătă: 10-12:30; duminică: Închis</t>
+  </si>
+  <si>
+    <t>luni: 07-09:30; marți: 07-09:30; miercuri: 07-09:30; joi: 07-09:30; vineri: 07-09:30; sâmbătă: 08-11:30; duminică: Închis</t>
+  </si>
+  <si>
+    <t>luni: 07-22; marți: 07-22; miercuri: 07-22; joi: 07-22; vineri: 07-22; sâmbătă: 07-22; duminică: 08-22</t>
+  </si>
+  <si>
+    <t>luni: 09-21; marți: 09-21; miercuri: 09-21; joi: 09-21; vineri: 09-21; sâmbătă: Închis; duminică: Închis</t>
+  </si>
+  <si>
+    <t>luni: 07:30-22; marți: 07:30-22; miercuri: 07:30-22; joi: 07:30-22; vineri: 07:30-22; sâmbătă: 09-19; duminică: 09-14</t>
+  </si>
+  <si>
+    <t>luni: 09-23; marți: 09-23; miercuri: 09-23; joi: 09-23; vineri: 09-23; sâmbătă: 10-16; duminică: 10-16</t>
+  </si>
+  <si>
+    <t>luni: 07-22; marți: 07-22; miercuri: 07-22; joi: 07-22; vineri: 07-22; sâmbătă: 08-21; duminică: 08-21</t>
+  </si>
+  <si>
+    <t>luni: 06:30-22; marți: 06:30-22; miercuri: 06:30-22; joi: 06:30-22; vineri: 06:30-22; sâmbătă: 08-21; duminică: 08-21</t>
+  </si>
+  <si>
+    <t>luni: 08-22; marți: 08-22; miercuri: 08-22; joi: 08-22; vineri: 08-22; sâmbătă: 08-20; duminică: 08-20</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
     <t>4.9</t>
   </si>
   <si>
     <t>5.0</t>
   </si>
   <si>
-    <t>4.6</t>
-  </si>
-  <si>
-    <t>4.4</t>
-  </si>
-  <si>
-    <t>4.7</t>
+    <t>4.5</t>
   </si>
   <si>
     <t>4.8</t>
@@ -1624,145 +1588,160 @@
     <t>3.9</t>
   </si>
   <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
     <t>4.2</t>
   </si>
   <si>
-    <t>4.5</t>
+    <t>899</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>709</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>766</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>3432</t>
+  </si>
+  <si>
+    <t>287</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>551</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>546</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>444</t>
+  </si>
+  <si>
+    <t>553</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>588</t>
+  </si>
+  <si>
+    <t>63</t>
   </si>
   <si>
     <t>132</t>
   </si>
   <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>435</t>
-  </si>
-  <si>
-    <t>899</t>
-  </si>
-  <si>
-    <t>289</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>709</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>950</t>
-  </si>
-  <si>
-    <t>766</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>368</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>3432</t>
-  </si>
-  <si>
-    <t>287</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>551</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>859</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>615</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>153</t>
-  </si>
-  <si>
-    <t>854</t>
-  </si>
-  <si>
-    <t>1155</t>
-  </si>
-  <si>
-    <t>133</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/fitnesshunedoara</t>
+    <t>155</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>745</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>362</t>
+  </si>
+  <si>
+    <t>549</t>
+  </si>
+  <si>
+    <t>355</t>
   </si>
   <si>
     <t>https://www.facebook.com/salsafitgym</t>
@@ -1771,18 +1750,6 @@
     <t>https://www.facebook.com/StayFitGym</t>
   </si>
   <si>
-    <t>https://www.facebook.com/befit.gym.romania</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/oxygengymoradea</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/SmartfitCetatii</t>
-  </si>
-  <si>
-    <t>https://facebook.com/rockgym.ro</t>
-  </si>
-  <si>
     <t>https://www.facebook.com/skyfitnessromana</t>
   </si>
   <si>
@@ -1795,25 +1762,49 @@
     <t>https://www.facebook.com/FreshClubAerobic</t>
   </si>
   <si>
-    <t>https://www.facebook.com/friendsarenatm</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/GymOne5</t>
-  </si>
-  <si>
     <t>https://www.facebook.com/sweatconcept</t>
   </si>
   <si>
-    <t>https://www.facebook.com/StudioCtheplace4U2B</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/Areagym.ro</t>
-  </si>
-  <si>
     <t>https://www.facebook.com/shapeupstudiounirii</t>
   </si>
   <si>
-    <t>https://www.instagram.com/fitness4allhd</t>
+    <t>https://www.facebook.com/FitnessPallady</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/AnturajFitness</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/onyx.fitnessclub</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/DownTownBucuresti</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/worldclass.romania</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/unisportscotroceni</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/humanfitnessclinic</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ladyfitgym</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/grooveboxRO</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/UzinaFitness</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/royalfitnesscluboficial</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/Bestfitnessgym</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/700FitClub</t>
   </si>
   <si>
     <t>https://www.instagram.com/salsafitgym</t>
@@ -1822,43 +1813,55 @@
     <t>https://www.instagram.com/stayfitgym_ro</t>
   </si>
   <si>
-    <t>https://www.instagram.com/be.fit.romania</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/alexiagoncan</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/oxygen_o2gym</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/dorupescarupersonaltrainer</t>
-  </si>
-  <si>
-    <t>https://instagram.com/therockgym.ro</t>
-  </si>
-  <si>
     <t>https://www.instagram.com/SkyFitnessRomana</t>
   </si>
   <si>
     <t>https://www.instagram.com/esx.ro</t>
   </si>
   <si>
-    <t>https://instagram.com/friendsarenatimisoara</t>
-  </si>
-  <si>
     <t>https://www.instagram.com/sweat.concept</t>
   </si>
   <si>
-    <t>https://www.instagram.com/areagym.ro</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/18gym.romania</t>
-  </si>
-  <si>
     <t>https://www.instagram.com/shapeupstudio</t>
   </si>
   <si>
-    <t>https://wa.me/40738711661</t>
+    <t>https://www.instagram.com/fitactivebucuresti_vitan</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/anturajfitness</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/onyx.fitnessclub</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/downtownfitness.ro</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/worldclass.romania</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/unisports_gym</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/humanfitnessclinic</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ladyfit.gym</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/groovebox.ro</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/Uzina_crossfitColumna</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/fitnessclubroyal</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bestfitnessgymbfg</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/700fitclub</t>
   </si>
   <si>
     <t>https://wa.me/40728947271</t>
@@ -1888,25 +1891,52 @@
     <t>https://www.youtube.com/@sweatchannel</t>
   </si>
   <si>
-    <t>https://www.youtube.com/@18gymromania</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/channel/UC6JigsM2N_zBr2SYZCl3y8A</t>
   </si>
   <si>
+    <t>https://www.youtube.com/@downtownfitnessbucuresti</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/user/WorldClassRomania</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/channel/UCaapP2KkuRABg7dFbVYpZ5w</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/channel/UCh_NIr9Zn2oM81td76SmqhA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@groovebox2014</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/channel/UCIFrpTGg6QT2etuKHFzcdNQ</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/channel/UCDfrhLnKV1V6uRSNrXAOOqQ</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/channel/UCbubTij6Hcr7WNjessiyfxQ</t>
+  </si>
+  <si>
     <t>https://www.tiktok.com/@stayfitgym_ro</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@befit.romania</t>
-  </si>
-  <si>
     <t>https://www.tiktok.com/@elitegymbucuresti</t>
   </si>
   <si>
-    <t>https://www.tiktok.com/@areagym.ro</t>
-  </si>
-  <si>
-    <t>https://www.tiktok.com/@18gymromania</t>
+    <t>https://www.tiktok.com/@fitactivebucurestivitan</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@downtownfitness.ro</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@unisportsgym</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@humanfitnessclinic</t>
+  </si>
+  <si>
+    <t>https://www.tiktok.com/@bestfitnessgym</t>
   </si>
 </sst>
 </file>
@@ -2353,52 +2383,43 @@
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" t="s">
-        <v>173</v>
+        <v>122</v>
       </c>
       <c r="F2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="G2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="H2" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="I2" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="K2" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="L2" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="N2" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="O2" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="P2" t="s">
-        <v>538</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>599</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -2409,43 +2430,55 @@
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F3" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="G3" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="H3" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="I3" t="s">
-        <v>288</v>
+        <v>263</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>313</v>
       </c>
       <c r="K3" t="s">
-        <v>372</v>
+        <v>357</v>
+      </c>
+      <c r="L3" t="s">
+        <v>406</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="N3" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="O3" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="P3" t="s">
-        <v>539</v>
+        <v>528</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>597</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -2456,43 +2489,46 @@
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F4" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="G4" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="H4" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="I4" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="K4" t="s">
-        <v>373</v>
+        <v>358</v>
+      </c>
+      <c r="L4" t="s">
+        <v>407</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="N4" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="O4" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="P4" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -2503,46 +2539,55 @@
         <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F5" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="G5" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="H5" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="I5" t="s">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="K5" t="s">
-        <v>374</v>
-      </c>
-      <c r="L5" t="s">
-        <v>418</v>
+        <v>359</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="N5" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="O5" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="P5" t="s">
-        <v>541</v>
+        <v>530</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -2553,43 +2598,46 @@
         <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>126</v>
+      </c>
+      <c r="E6" t="s">
+        <v>175</v>
       </c>
       <c r="F6" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G6" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H6" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="I6" t="s">
-        <v>291</v>
+        <v>266</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="K6" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="L6" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="N6" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="O6" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="P6" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -2600,55 +2648,43 @@
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F7" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G7" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H7" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="I7" t="s">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="K7" t="s">
-        <v>376</v>
-      </c>
-      <c r="L7" t="s">
-        <v>420</v>
+        <v>361</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="N7" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="O7" t="s">
-        <v>531</v>
+        <v>517</v>
       </c>
       <c r="P7" t="s">
-        <v>543</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>615</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -2659,46 +2695,43 @@
         <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F8" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G8" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H8" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="I8" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="K8" t="s">
-        <v>377</v>
-      </c>
-      <c r="L8" t="s">
-        <v>421</v>
+        <v>362</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="N8" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="O8" t="s">
+        <v>520</v>
+      </c>
+      <c r="P8" t="s">
         <v>533</v>
-      </c>
-      <c r="P8" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -2709,55 +2742,52 @@
         <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F9" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G9" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H9" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="I9" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="K9" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="N9" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="O9" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="P9" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>626</v>
+        <v>599</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -2768,46 +2798,37 @@
         <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F10" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G10" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H10" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="I10" t="s">
-        <v>295</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>343</v>
+        <v>270</v>
       </c>
       <c r="K10" t="s">
-        <v>379</v>
-      </c>
-      <c r="L10" t="s">
-        <v>422</v>
+        <v>364</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="N10" t="s">
-        <v>497</v>
+        <v>435</v>
       </c>
       <c r="O10" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="P10" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -2818,55 +2839,49 @@
         <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F11" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="G11" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="H11" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="I11" t="s">
-        <v>296</v>
+        <v>271</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="K11" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="L11" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="N11" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="O11" t="s">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="P11" t="s">
-        <v>547</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>627</v>
+        <v>536</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -2877,37 +2892,49 @@
         <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F12" t="s">
+        <v>211</v>
+      </c>
+      <c r="G12" t="s">
+        <v>211</v>
+      </c>
+      <c r="H12" t="s">
         <v>222</v>
       </c>
-      <c r="G12" t="s">
-        <v>231</v>
-      </c>
-      <c r="H12" t="s">
-        <v>248</v>
-      </c>
       <c r="I12" t="s">
-        <v>297</v>
-      </c>
-      <c r="K12" t="s">
-        <v>381</v>
+        <v>272</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>450</v>
+        <v>437</v>
+      </c>
+      <c r="N12" t="s">
+        <v>477</v>
       </c>
       <c r="O12" t="s">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="P12" t="s">
-        <v>548</v>
+        <v>537</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -2918,49 +2945,49 @@
         <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F13" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="G13" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="H13" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="I13" t="s">
-        <v>298</v>
+        <v>273</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="K13" t="s">
-        <v>382</v>
-      </c>
-      <c r="L13" t="s">
-        <v>424</v>
+        <v>366</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="N13" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="O13" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="P13" t="s">
-        <v>549</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>603</v>
+        <v>538</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -2971,52 +2998,52 @@
         <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F14" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="G14" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="H14" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="I14" t="s">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="K14" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="L14" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="N14" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="O14" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="P14" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>604</v>
+        <v>581</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -3027,40 +3054,46 @@
         <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F15" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="G15" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="H15" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="I15" t="s">
-        <v>300</v>
+        <v>275</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>324</v>
       </c>
       <c r="K15" t="s">
-        <v>384</v>
+        <v>368</v>
+      </c>
+      <c r="L15" t="s">
+        <v>411</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="N15" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="O15" t="s">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="P15" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -3071,52 +3104,49 @@
         <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
-        <v>137</v>
-      </c>
-      <c r="E16" t="s">
-        <v>186</v>
+        <v>136</v>
       </c>
       <c r="F16" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="G16" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H16" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="I16" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="K16" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="L16" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="N16" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="O16" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="P16" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>605</v>
+        <v>579</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -3127,37 +3157,46 @@
         <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E17" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F17" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="G17" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H17" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="I17" t="s">
-        <v>302</v>
+        <v>277</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="K17" t="s">
+        <v>370</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="N17" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="O17" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="P17" t="s">
-        <v>553</v>
+        <v>542</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -3168,43 +3207,55 @@
         <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E18" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F18" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="G18" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H18" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="I18" t="s">
-        <v>303</v>
+        <v>278</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="K18" t="s">
-        <v>386</v>
+        <v>371</v>
+      </c>
+      <c r="L18" t="s">
+        <v>413</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="N18" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="O18" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="P18" t="s">
-        <v>554</v>
+        <v>543</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -3215,55 +3266,55 @@
         <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E19" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F19" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="G19" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H19" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="I19" t="s">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="K19" t="s">
-        <v>387</v>
+        <v>372</v>
+      </c>
+      <c r="L19" t="s">
+        <v>413</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="N19" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="O19" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="P19" t="s">
-        <v>555</v>
+        <v>528</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="R19" s="2" t="s">
         <v>601</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -3274,40 +3325,55 @@
         <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E20" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="F20" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="G20" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H20" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="I20" t="s">
-        <v>305</v>
+        <v>280</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="K20" t="s">
-        <v>388</v>
+        <v>373</v>
+      </c>
+      <c r="L20" t="s">
+        <v>414</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="N20" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="O20" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="P20" t="s">
-        <v>556</v>
+        <v>544</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -3318,40 +3384,52 @@
         <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E21" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F21" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="G21" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="H21" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="I21" t="s">
-        <v>306</v>
+        <v>281</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="K21" t="s">
-        <v>389</v>
+        <v>374</v>
+      </c>
+      <c r="L21" t="s">
+        <v>415</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="N21" t="s">
-        <v>506</v>
+        <v>477</v>
       </c>
       <c r="O21" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="P21" t="s">
-        <v>557</v>
+        <v>545</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -3362,52 +3440,43 @@
         <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E22" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F22" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="G22" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="H22" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="I22" t="s">
-        <v>307</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>349</v>
+        <v>282</v>
       </c>
       <c r="K22" t="s">
-        <v>390</v>
-      </c>
-      <c r="L22" t="s">
-        <v>427</v>
+        <v>375</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="N22" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="O22" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="P22" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>606</v>
+        <v>584</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -3418,43 +3487,52 @@
         <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E23" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F23" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G23" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H23" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="I23" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="K23" t="s">
-        <v>391</v>
+        <v>376</v>
+      </c>
+      <c r="L23" t="s">
+        <v>416</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="N23" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="O23" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="P23" t="s">
-        <v>559</v>
+        <v>547</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -3465,43 +3543,49 @@
         <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E24" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F24" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G24" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H24" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="I24" t="s">
-        <v>309</v>
+        <v>284</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="K24" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="N24" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="O24" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="P24" t="s">
-        <v>560</v>
+        <v>548</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -3512,52 +3596,43 @@
         <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E25" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F25" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G25" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H25" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="I25" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="K25" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="N25" t="s">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="O25" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="P25" t="s">
-        <v>561</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>616</v>
+        <v>549</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -3568,37 +3643,43 @@
         <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D26" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E26" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F26" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G26" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H26" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="I26" t="s">
-        <v>311</v>
+        <v>286</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>334</v>
       </c>
       <c r="K26" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>464</v>
+        <v>451</v>
+      </c>
+      <c r="N26" t="s">
+        <v>496</v>
       </c>
       <c r="O26" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="P26" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -3609,49 +3690,58 @@
         <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E27" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F27" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G27" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H27" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="I27" t="s">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="K27" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="L27" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="N27" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="O27" t="s">
-        <v>531</v>
+        <v>517</v>
       </c>
       <c r="P27" t="s">
-        <v>563</v>
-      </c>
-      <c r="S27" s="2" t="s">
-        <v>617</v>
+        <v>551</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -3662,49 +3752,55 @@
         <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D28" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E28" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F28" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G28" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H28" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="I28" t="s">
-        <v>313</v>
+        <v>288</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>354</v>
+        <v>336</v>
+      </c>
+      <c r="K28" t="s">
+        <v>381</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="N28" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="O28" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="P28" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="T28" s="2" t="s">
         <v>620</v>
+      </c>
+      <c r="U28" s="2" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -3715,49 +3811,52 @@
         <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E29" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F29" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G29" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H29" t="s">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="I29" t="s">
-        <v>314</v>
+        <v>289</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="K29" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="N29" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="O29" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="P29" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="S29" s="2" t="s">
-        <v>618</v>
+        <v>588</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -3768,40 +3867,58 @@
         <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E30" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F30" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G30" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="H30" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="I30" t="s">
-        <v>315</v>
+        <v>290</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="K30" t="s">
-        <v>397</v>
+        <v>383</v>
+      </c>
+      <c r="L30" t="s">
+        <v>418</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="N30" t="s">
-        <v>513</v>
+        <v>480</v>
       </c>
       <c r="O30" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="P30" t="s">
-        <v>566</v>
+        <v>554</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -3812,46 +3929,52 @@
         <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E31" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F31" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="G31" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="H31" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="I31" t="s">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="K31" t="s">
-        <v>398</v>
-      </c>
-      <c r="L31" t="s">
-        <v>429</v>
+        <v>384</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="N31" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="O31" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="P31" t="s">
-        <v>567</v>
+        <v>555</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="U31" s="2" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -3865,40 +3988,43 @@
         <v>121</v>
       </c>
       <c r="D32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E32" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F32" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="G32" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="H32" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="I32" t="s">
-        <v>317</v>
+        <v>292</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="K32" t="s">
-        <v>399</v>
+        <v>385</v>
+      </c>
+      <c r="L32" t="s">
+        <v>419</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="N32" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="O32" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="P32" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -3909,52 +4035,58 @@
         <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E33" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F33" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G33" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H33" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="I33" t="s">
-        <v>318</v>
+        <v>293</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="K33" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="L33" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="N33" t="s">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="O33" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="P33" t="s">
         <v>557</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>609</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>621</v>
+        <v>628</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="34" spans="1:21">
@@ -3962,49 +4094,58 @@
         <v>53</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E34" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F34" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G34" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H34" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="I34" t="s">
-        <v>319</v>
+        <v>294</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="K34" t="s">
-        <v>401</v>
-      </c>
-      <c r="L34" t="s">
-        <v>431</v>
+        <v>387</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="N34" t="s">
+        <v>480</v>
+      </c>
+      <c r="O34" t="s">
         <v>516</v>
       </c>
-      <c r="O34" t="s">
-        <v>531</v>
-      </c>
       <c r="P34" t="s">
-        <v>569</v>
+        <v>558</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="U34" s="2" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="35" spans="1:21">
@@ -4012,52 +4153,55 @@
         <v>54</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D35" t="s">
-        <v>156</v>
+        <v>155</v>
+      </c>
+      <c r="E35" t="s">
+        <v>201</v>
       </c>
       <c r="F35" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G35" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H35" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="I35" t="s">
-        <v>320</v>
+        <v>295</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="K35" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="L35" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="N35" t="s">
-        <v>517</v>
+        <v>460</v>
       </c>
       <c r="O35" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="P35" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>610</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
     </row>
     <row r="36" spans="1:21">
@@ -4065,49 +4209,46 @@
         <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E36" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="F36" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G36" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H36" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="I36" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="K36" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="N36" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="O36" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="P36" t="s">
-        <v>571</v>
-      </c>
-      <c r="U36" s="2" t="s">
-        <v>628</v>
+        <v>560</v>
       </c>
     </row>
     <row r="37" spans="1:21">
@@ -4115,55 +4256,61 @@
         <v>56</v>
       </c>
       <c r="B37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E37" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F37" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="G37" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="H37" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="I37" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="K37" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="L37" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="N37" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="O37" t="s">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="P37" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
+      </c>
+      <c r="T37" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="U37" s="2" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="38" spans="1:21">
@@ -4171,49 +4318,61 @@
         <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D38" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E38" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="F38" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="G38" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="H38" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="I38" t="s">
-        <v>323</v>
+        <v>298</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="K38" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="L38" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="N38" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="O38" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="P38" t="s">
-        <v>572</v>
+        <v>562</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="39" spans="1:21">
@@ -4221,46 +4380,61 @@
         <v>58</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D39" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E39" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F39" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="G39" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="H39" t="s">
-        <v>275</v>
+        <v>249</v>
       </c>
       <c r="I39" t="s">
-        <v>324</v>
+        <v>299</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>347</v>
       </c>
       <c r="K39" t="s">
-        <v>406</v>
+        <v>392</v>
+      </c>
+      <c r="L39" t="s">
+        <v>417</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="N39" t="s">
-        <v>520</v>
+        <v>497</v>
       </c>
       <c r="O39" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="P39" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>594</v>
+        <v>587</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="T39" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="U39" s="2" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="40" spans="1:21">
@@ -4268,40 +4442,43 @@
         <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E40" t="s">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="F40" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="G40" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="H40" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="I40" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="K40" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>478</v>
+        <v>465</v>
+      </c>
+      <c r="N40" t="s">
+        <v>505</v>
       </c>
       <c r="O40" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="P40" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
     </row>
     <row r="41" spans="1:21">
@@ -4309,40 +4486,58 @@
         <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D41" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E41" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F41" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="G41" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="H41" t="s">
-        <v>277</v>
+        <v>251</v>
       </c>
       <c r="I41" t="s">
-        <v>326</v>
+        <v>301</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="K41" t="s">
+        <v>394</v>
+      </c>
+      <c r="L41" t="s">
+        <v>422</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="N41" t="s">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="O41" t="s">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="P41" t="s">
-        <v>574</v>
+        <v>565</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="T41" s="2" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="42" spans="1:21">
@@ -4350,43 +4545,58 @@
         <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D42" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E42" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="F42" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G42" t="s">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="H42" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="I42" t="s">
-        <v>327</v>
+        <v>302</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>349</v>
       </c>
       <c r="K42" t="s">
-        <v>408</v>
+        <v>395</v>
+      </c>
+      <c r="L42" t="s">
+        <v>423</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="N42" t="s">
+        <v>507</v>
+      </c>
+      <c r="O42" t="s">
         <v>522</v>
       </c>
-      <c r="O42" t="s">
-        <v>529</v>
-      </c>
       <c r="P42" t="s">
-        <v>575</v>
+        <v>566</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="T42" s="2" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="43" spans="1:21">
@@ -4394,49 +4604,46 @@
         <v>62</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D43" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E43" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="F43" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G43" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H43" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="I43" t="s">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="K43" t="s">
-        <v>409</v>
-      </c>
-      <c r="L43" t="s">
-        <v>435</v>
+        <v>396</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="N43" t="s">
-        <v>523</v>
+        <v>508</v>
       </c>
       <c r="O43" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="P43" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
     </row>
     <row r="44" spans="1:21">
@@ -4444,58 +4651,58 @@
         <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D44" t="s">
-        <v>165</v>
-      </c>
-      <c r="E44" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="F44" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G44" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H44" t="s">
-        <v>280</v>
+        <v>254</v>
       </c>
       <c r="I44" t="s">
-        <v>329</v>
+        <v>304</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="K44" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="L44" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="N44" t="s">
-        <v>524</v>
+        <v>480</v>
       </c>
       <c r="O44" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="P44" t="s">
+        <v>568</v>
+      </c>
+      <c r="Q44" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="Q44" s="2" t="s">
-        <v>595</v>
-      </c>
       <c r="R44" s="2" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
+      </c>
+      <c r="U44" s="2" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="45" spans="1:21">
@@ -4503,58 +4710,43 @@
         <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C45" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D45" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E45" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="F45" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G45" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H45" t="s">
-        <v>281</v>
+        <v>255</v>
       </c>
       <c r="I45" t="s">
-        <v>330</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>366</v>
+        <v>305</v>
       </c>
       <c r="K45" t="s">
-        <v>411</v>
-      </c>
-      <c r="L45" t="s">
-        <v>436</v>
+        <v>398</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="N45" t="s">
-        <v>524</v>
+        <v>509</v>
       </c>
       <c r="O45" t="s">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="P45" t="s">
-        <v>543</v>
-      </c>
-      <c r="Q45" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="R45" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="T45" s="2" t="s">
-        <v>623</v>
+        <v>569</v>
       </c>
     </row>
     <row r="46" spans="1:21">
@@ -4562,52 +4754,52 @@
         <v>65</v>
       </c>
       <c r="B46" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C46" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D46" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E46" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="F46" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="G46" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="H46" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="I46" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="K46" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="L46" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="N46" t="s">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="O46" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="P46" t="s">
-        <v>578</v>
-      </c>
-      <c r="Q46" s="2" t="s">
-        <v>596</v>
+        <v>570</v>
+      </c>
+      <c r="T46" s="2" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="47" spans="1:21">
@@ -4615,58 +4807,55 @@
         <v>66</v>
       </c>
       <c r="B47" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C47" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D47" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E47" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F47" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="G47" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="H47" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="I47" t="s">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="K47" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="L47" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="N47" t="s">
-        <v>526</v>
+        <v>511</v>
       </c>
       <c r="O47" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="P47" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="U47" s="2" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
     </row>
     <row r="48" spans="1:21">
@@ -4674,55 +4863,52 @@
         <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D48" t="s">
-        <v>169</v>
-      </c>
-      <c r="E48" t="s">
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="F48" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="G48" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="H48" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="I48" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="K48" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="N48" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="O48" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="P48" t="s">
-        <v>580</v>
+        <v>572</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>595</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="T48" s="2" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="U48" s="2" t="s">
-        <v>630</v>
+        <v>640</v>
       </c>
     </row>
     <row r="49" spans="1:20">
@@ -4730,40 +4916,52 @@
         <v>68</v>
       </c>
       <c r="B49" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C49" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D49" t="s">
-        <v>170</v>
-      </c>
-      <c r="E49" t="s">
-        <v>217</v>
+        <v>169</v>
       </c>
       <c r="F49" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="G49" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="H49" t="s">
-        <v>284</v>
+        <v>259</v>
       </c>
       <c r="I49" t="s">
-        <v>333</v>
+        <v>309</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="K49" t="s">
+        <v>402</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="N49" t="s">
-        <v>527</v>
+        <v>513</v>
       </c>
       <c r="O49" t="s">
-        <v>537</v>
+        <v>517</v>
       </c>
       <c r="P49" t="s">
-        <v>581</v>
+        <v>573</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="R49" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="T49" s="2" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="50" spans="1:20">
@@ -4771,43 +4969,55 @@
         <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C50" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E50" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="F50" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="G50" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="H50" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="I50" t="s">
-        <v>334</v>
+        <v>310</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>355</v>
       </c>
       <c r="K50" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="N50" t="s">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="O50" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="P50" t="s">
-        <v>540</v>
+        <v>574</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="R50" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="T50" s="2" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="51" spans="1:20">
@@ -4815,205 +5025,242 @@
         <v>70</v>
       </c>
       <c r="B51" t="s">
+        <v>119</v>
+      </c>
+      <c r="C51" t="s">
         <v>120</v>
       </c>
-      <c r="C51" t="s">
-        <v>121</v>
-      </c>
       <c r="D51" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E51" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="F51" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G51" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H51" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
       <c r="I51" t="s">
-        <v>335</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>370</v>
+        <v>311</v>
       </c>
       <c r="K51" t="s">
-        <v>416</v>
-      </c>
-      <c r="L51" t="s">
-        <v>439</v>
+        <v>404</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="N51" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="O51" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="P51" t="s">
-        <v>553</v>
-      </c>
-      <c r="Q51" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="R51" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="T51" s="2" t="s">
-        <v>625</v>
+        <v>575</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="J2" r:id="rId1"/>
     <hyperlink ref="M2" r:id="rId2"/>
-    <hyperlink ref="Q2" r:id="rId3"/>
-    <hyperlink ref="R2" r:id="rId4"/>
-    <hyperlink ref="M3" r:id="rId5"/>
-    <hyperlink ref="S3" r:id="rId6"/>
-    <hyperlink ref="J4" r:id="rId7"/>
-    <hyperlink ref="M4" r:id="rId8"/>
-    <hyperlink ref="J5" r:id="rId9"/>
-    <hyperlink ref="M5" r:id="rId10"/>
-    <hyperlink ref="J6" r:id="rId11"/>
-    <hyperlink ref="M6" r:id="rId12"/>
-    <hyperlink ref="J7" r:id="rId13"/>
-    <hyperlink ref="M7" r:id="rId14"/>
-    <hyperlink ref="Q7" r:id="rId15"/>
-    <hyperlink ref="R7" r:id="rId16"/>
-    <hyperlink ref="S7" r:id="rId17"/>
-    <hyperlink ref="J8" r:id="rId18"/>
-    <hyperlink ref="M8" r:id="rId19"/>
-    <hyperlink ref="J9" r:id="rId20"/>
-    <hyperlink ref="M9" r:id="rId21"/>
-    <hyperlink ref="Q9" r:id="rId22"/>
-    <hyperlink ref="R9" r:id="rId23"/>
-    <hyperlink ref="T9" r:id="rId24"/>
-    <hyperlink ref="U9" r:id="rId25"/>
-    <hyperlink ref="J10" r:id="rId26"/>
+    <hyperlink ref="J3" r:id="rId3"/>
+    <hyperlink ref="M3" r:id="rId4"/>
+    <hyperlink ref="Q3" r:id="rId5"/>
+    <hyperlink ref="R3" r:id="rId6"/>
+    <hyperlink ref="S3" r:id="rId7"/>
+    <hyperlink ref="J4" r:id="rId8"/>
+    <hyperlink ref="M4" r:id="rId9"/>
+    <hyperlink ref="J5" r:id="rId10"/>
+    <hyperlink ref="M5" r:id="rId11"/>
+    <hyperlink ref="Q5" r:id="rId12"/>
+    <hyperlink ref="R5" r:id="rId13"/>
+    <hyperlink ref="T5" r:id="rId14"/>
+    <hyperlink ref="U5" r:id="rId15"/>
+    <hyperlink ref="J6" r:id="rId16"/>
+    <hyperlink ref="M6" r:id="rId17"/>
+    <hyperlink ref="J7" r:id="rId18"/>
+    <hyperlink ref="M7" r:id="rId19"/>
+    <hyperlink ref="J8" r:id="rId20"/>
+    <hyperlink ref="M8" r:id="rId21"/>
+    <hyperlink ref="J9" r:id="rId22"/>
+    <hyperlink ref="M9" r:id="rId23"/>
+    <hyperlink ref="Q9" r:id="rId24"/>
+    <hyperlink ref="R9" r:id="rId25"/>
+    <hyperlink ref="S9" r:id="rId26"/>
     <hyperlink ref="M10" r:id="rId27"/>
     <hyperlink ref="J11" r:id="rId28"/>
     <hyperlink ref="M11" r:id="rId29"/>
-    <hyperlink ref="Q11" r:id="rId30"/>
-    <hyperlink ref="R11" r:id="rId31"/>
-    <hyperlink ref="U11" r:id="rId32"/>
-    <hyperlink ref="M12" r:id="rId33"/>
-    <hyperlink ref="J13" r:id="rId34"/>
-    <hyperlink ref="M13" r:id="rId35"/>
-    <hyperlink ref="R13" r:id="rId36"/>
-    <hyperlink ref="J14" r:id="rId37"/>
-    <hyperlink ref="M14" r:id="rId38"/>
-    <hyperlink ref="Q14" r:id="rId39"/>
-    <hyperlink ref="R14" r:id="rId40"/>
-    <hyperlink ref="M15" r:id="rId41"/>
-    <hyperlink ref="J16" r:id="rId42"/>
-    <hyperlink ref="M16" r:id="rId43"/>
-    <hyperlink ref="Q16" r:id="rId44"/>
-    <hyperlink ref="R16" r:id="rId45"/>
-    <hyperlink ref="M17" r:id="rId46"/>
-    <hyperlink ref="J18" r:id="rId47"/>
-    <hyperlink ref="M18" r:id="rId48"/>
-    <hyperlink ref="J19" r:id="rId49"/>
-    <hyperlink ref="M19" r:id="rId50"/>
-    <hyperlink ref="Q19" r:id="rId51"/>
-    <hyperlink ref="R19" r:id="rId52"/>
-    <hyperlink ref="T19" r:id="rId53"/>
-    <hyperlink ref="U19" r:id="rId54"/>
-    <hyperlink ref="M20" r:id="rId55"/>
-    <hyperlink ref="M21" r:id="rId56"/>
-    <hyperlink ref="J22" r:id="rId57"/>
-    <hyperlink ref="M22" r:id="rId58"/>
-    <hyperlink ref="Q22" r:id="rId59"/>
-    <hyperlink ref="R22" r:id="rId60"/>
-    <hyperlink ref="J23" r:id="rId61"/>
-    <hyperlink ref="M23" r:id="rId62"/>
-    <hyperlink ref="J24" r:id="rId63"/>
-    <hyperlink ref="M24" r:id="rId64"/>
-    <hyperlink ref="J25" r:id="rId65"/>
-    <hyperlink ref="M25" r:id="rId66"/>
-    <hyperlink ref="Q25" r:id="rId67"/>
-    <hyperlink ref="R25" r:id="rId68"/>
-    <hyperlink ref="S25" r:id="rId69"/>
-    <hyperlink ref="M26" r:id="rId70"/>
-    <hyperlink ref="J27" r:id="rId71"/>
-    <hyperlink ref="M27" r:id="rId72"/>
-    <hyperlink ref="S27" r:id="rId73"/>
-    <hyperlink ref="J28" r:id="rId74"/>
-    <hyperlink ref="M28" r:id="rId75"/>
-    <hyperlink ref="Q28" r:id="rId76"/>
-    <hyperlink ref="R28" r:id="rId77"/>
-    <hyperlink ref="T28" r:id="rId78"/>
-    <hyperlink ref="J29" r:id="rId79"/>
-    <hyperlink ref="M29" r:id="rId80"/>
-    <hyperlink ref="Q29" r:id="rId81"/>
-    <hyperlink ref="S29" r:id="rId82"/>
-    <hyperlink ref="M30" r:id="rId83"/>
-    <hyperlink ref="J31" r:id="rId84"/>
-    <hyperlink ref="M31" r:id="rId85"/>
-    <hyperlink ref="J32" r:id="rId86"/>
-    <hyperlink ref="M32" r:id="rId87"/>
-    <hyperlink ref="J33" r:id="rId88"/>
-    <hyperlink ref="M33" r:id="rId89"/>
-    <hyperlink ref="Q33" r:id="rId90"/>
-    <hyperlink ref="T33" r:id="rId91"/>
-    <hyperlink ref="J34" r:id="rId92"/>
-    <hyperlink ref="M34" r:id="rId93"/>
-    <hyperlink ref="J35" r:id="rId94"/>
-    <hyperlink ref="M35" r:id="rId95"/>
-    <hyperlink ref="Q35" r:id="rId96"/>
-    <hyperlink ref="T35" r:id="rId97"/>
-    <hyperlink ref="J36" r:id="rId98"/>
-    <hyperlink ref="M36" r:id="rId99"/>
-    <hyperlink ref="U36" r:id="rId100"/>
-    <hyperlink ref="J37" r:id="rId101"/>
-    <hyperlink ref="M37" r:id="rId102"/>
-    <hyperlink ref="Q37" r:id="rId103"/>
-    <hyperlink ref="R37" r:id="rId104"/>
-    <hyperlink ref="J38" r:id="rId105"/>
-    <hyperlink ref="M38" r:id="rId106"/>
-    <hyperlink ref="M39" r:id="rId107"/>
-    <hyperlink ref="Q39" r:id="rId108"/>
-    <hyperlink ref="M40" r:id="rId109"/>
-    <hyperlink ref="M41" r:id="rId110"/>
-    <hyperlink ref="M42" r:id="rId111"/>
-    <hyperlink ref="J43" r:id="rId112"/>
-    <hyperlink ref="M43" r:id="rId113"/>
-    <hyperlink ref="J44" r:id="rId114"/>
-    <hyperlink ref="M44" r:id="rId115"/>
-    <hyperlink ref="Q44" r:id="rId116"/>
-    <hyperlink ref="R44" r:id="rId117"/>
-    <hyperlink ref="T44" r:id="rId118"/>
-    <hyperlink ref="J45" r:id="rId119"/>
-    <hyperlink ref="M45" r:id="rId120"/>
-    <hyperlink ref="Q45" r:id="rId121"/>
-    <hyperlink ref="R45" r:id="rId122"/>
-    <hyperlink ref="T45" r:id="rId123"/>
-    <hyperlink ref="J46" r:id="rId124"/>
-    <hyperlink ref="M46" r:id="rId125"/>
-    <hyperlink ref="Q46" r:id="rId126"/>
-    <hyperlink ref="J47" r:id="rId127"/>
-    <hyperlink ref="M47" r:id="rId128"/>
-    <hyperlink ref="Q47" r:id="rId129"/>
-    <hyperlink ref="R47" r:id="rId130"/>
-    <hyperlink ref="U47" r:id="rId131"/>
-    <hyperlink ref="J48" r:id="rId132"/>
-    <hyperlink ref="M48" r:id="rId133"/>
-    <hyperlink ref="R48" r:id="rId134"/>
-    <hyperlink ref="T48" r:id="rId135"/>
-    <hyperlink ref="U48" r:id="rId136"/>
-    <hyperlink ref="M49" r:id="rId137"/>
-    <hyperlink ref="M50" r:id="rId138"/>
-    <hyperlink ref="J51" r:id="rId139"/>
-    <hyperlink ref="M51" r:id="rId140"/>
-    <hyperlink ref="Q51" r:id="rId141"/>
-    <hyperlink ref="R51" r:id="rId142"/>
-    <hyperlink ref="T51" r:id="rId143"/>
+    <hyperlink ref="S11" r:id="rId30"/>
+    <hyperlink ref="J12" r:id="rId31"/>
+    <hyperlink ref="M12" r:id="rId32"/>
+    <hyperlink ref="Q12" r:id="rId33"/>
+    <hyperlink ref="R12" r:id="rId34"/>
+    <hyperlink ref="T12" r:id="rId35"/>
+    <hyperlink ref="J13" r:id="rId36"/>
+    <hyperlink ref="M13" r:id="rId37"/>
+    <hyperlink ref="Q13" r:id="rId38"/>
+    <hyperlink ref="S13" r:id="rId39"/>
+    <hyperlink ref="J14" r:id="rId40"/>
+    <hyperlink ref="M14" r:id="rId41"/>
+    <hyperlink ref="Q14" r:id="rId42"/>
+    <hyperlink ref="T14" r:id="rId43"/>
+    <hyperlink ref="J15" r:id="rId44"/>
+    <hyperlink ref="M15" r:id="rId45"/>
+    <hyperlink ref="J16" r:id="rId46"/>
+    <hyperlink ref="M16" r:id="rId47"/>
+    <hyperlink ref="Q16" r:id="rId48"/>
+    <hyperlink ref="T16" r:id="rId49"/>
+    <hyperlink ref="J17" r:id="rId50"/>
+    <hyperlink ref="M17" r:id="rId51"/>
+    <hyperlink ref="U17" r:id="rId52"/>
+    <hyperlink ref="J18" r:id="rId53"/>
+    <hyperlink ref="M18" r:id="rId54"/>
+    <hyperlink ref="Q18" r:id="rId55"/>
+    <hyperlink ref="R18" r:id="rId56"/>
+    <hyperlink ref="T18" r:id="rId57"/>
+    <hyperlink ref="J19" r:id="rId58"/>
+    <hyperlink ref="M19" r:id="rId59"/>
+    <hyperlink ref="Q19" r:id="rId60"/>
+    <hyperlink ref="R19" r:id="rId61"/>
+    <hyperlink ref="T19" r:id="rId62"/>
+    <hyperlink ref="J20" r:id="rId63"/>
+    <hyperlink ref="M20" r:id="rId64"/>
+    <hyperlink ref="Q20" r:id="rId65"/>
+    <hyperlink ref="R20" r:id="rId66"/>
+    <hyperlink ref="T20" r:id="rId67"/>
+    <hyperlink ref="J21" r:id="rId68"/>
+    <hyperlink ref="M21" r:id="rId69"/>
+    <hyperlink ref="R21" r:id="rId70"/>
+    <hyperlink ref="U21" r:id="rId71"/>
+    <hyperlink ref="M22" r:id="rId72"/>
+    <hyperlink ref="Q22" r:id="rId73"/>
+    <hyperlink ref="J23" r:id="rId74"/>
+    <hyperlink ref="M23" r:id="rId75"/>
+    <hyperlink ref="Q23" r:id="rId76"/>
+    <hyperlink ref="R23" r:id="rId77"/>
+    <hyperlink ref="J24" r:id="rId78"/>
+    <hyperlink ref="M24" r:id="rId79"/>
+    <hyperlink ref="Q24" r:id="rId80"/>
+    <hyperlink ref="R24" r:id="rId81"/>
+    <hyperlink ref="J25" r:id="rId82"/>
+    <hyperlink ref="M25" r:id="rId83"/>
+    <hyperlink ref="J26" r:id="rId84"/>
+    <hyperlink ref="M26" r:id="rId85"/>
+    <hyperlink ref="J27" r:id="rId86"/>
+    <hyperlink ref="M27" r:id="rId87"/>
+    <hyperlink ref="Q27" r:id="rId88"/>
+    <hyperlink ref="R27" r:id="rId89"/>
+    <hyperlink ref="T27" r:id="rId90"/>
+    <hyperlink ref="U27" r:id="rId91"/>
+    <hyperlink ref="J28" r:id="rId92"/>
+    <hyperlink ref="M28" r:id="rId93"/>
+    <hyperlink ref="Q28" r:id="rId94"/>
+    <hyperlink ref="R28" r:id="rId95"/>
+    <hyperlink ref="T28" r:id="rId96"/>
+    <hyperlink ref="U28" r:id="rId97"/>
+    <hyperlink ref="J29" r:id="rId98"/>
+    <hyperlink ref="M29" r:id="rId99"/>
+    <hyperlink ref="Q29" r:id="rId100"/>
+    <hyperlink ref="R29" r:id="rId101"/>
+    <hyperlink ref="T29" r:id="rId102"/>
+    <hyperlink ref="J30" r:id="rId103"/>
+    <hyperlink ref="M30" r:id="rId104"/>
+    <hyperlink ref="Q30" r:id="rId105"/>
+    <hyperlink ref="R30" r:id="rId106"/>
+    <hyperlink ref="T30" r:id="rId107"/>
+    <hyperlink ref="U30" r:id="rId108"/>
+    <hyperlink ref="J31" r:id="rId109"/>
+    <hyperlink ref="M31" r:id="rId110"/>
+    <hyperlink ref="Q31" r:id="rId111"/>
+    <hyperlink ref="R31" r:id="rId112"/>
+    <hyperlink ref="U31" r:id="rId113"/>
+    <hyperlink ref="J32" r:id="rId114"/>
+    <hyperlink ref="M32" r:id="rId115"/>
+    <hyperlink ref="J33" r:id="rId116"/>
+    <hyperlink ref="M33" r:id="rId117"/>
+    <hyperlink ref="Q33" r:id="rId118"/>
+    <hyperlink ref="R33" r:id="rId119"/>
+    <hyperlink ref="T33" r:id="rId120"/>
+    <hyperlink ref="U33" r:id="rId121"/>
+    <hyperlink ref="J34" r:id="rId122"/>
+    <hyperlink ref="M34" r:id="rId123"/>
+    <hyperlink ref="Q34" r:id="rId124"/>
+    <hyperlink ref="R34" r:id="rId125"/>
+    <hyperlink ref="T34" r:id="rId126"/>
+    <hyperlink ref="U34" r:id="rId127"/>
+    <hyperlink ref="J35" r:id="rId128"/>
+    <hyperlink ref="M35" r:id="rId129"/>
+    <hyperlink ref="Q35" r:id="rId130"/>
+    <hyperlink ref="R35" r:id="rId131"/>
+    <hyperlink ref="T35" r:id="rId132"/>
+    <hyperlink ref="J36" r:id="rId133"/>
+    <hyperlink ref="M36" r:id="rId134"/>
+    <hyperlink ref="J37" r:id="rId135"/>
+    <hyperlink ref="M37" r:id="rId136"/>
+    <hyperlink ref="Q37" r:id="rId137"/>
+    <hyperlink ref="R37" r:id="rId138"/>
+    <hyperlink ref="T37" r:id="rId139"/>
+    <hyperlink ref="U37" r:id="rId140"/>
+    <hyperlink ref="J38" r:id="rId141"/>
+    <hyperlink ref="M38" r:id="rId142"/>
+    <hyperlink ref="Q38" r:id="rId143"/>
+    <hyperlink ref="R38" r:id="rId144"/>
+    <hyperlink ref="T38" r:id="rId145"/>
+    <hyperlink ref="U38" r:id="rId146"/>
+    <hyperlink ref="J39" r:id="rId147"/>
+    <hyperlink ref="M39" r:id="rId148"/>
+    <hyperlink ref="Q39" r:id="rId149"/>
+    <hyperlink ref="R39" r:id="rId150"/>
+    <hyperlink ref="T39" r:id="rId151"/>
+    <hyperlink ref="U39" r:id="rId152"/>
+    <hyperlink ref="M40" r:id="rId153"/>
+    <hyperlink ref="J41" r:id="rId154"/>
+    <hyperlink ref="M41" r:id="rId155"/>
+    <hyperlink ref="Q41" r:id="rId156"/>
+    <hyperlink ref="R41" r:id="rId157"/>
+    <hyperlink ref="T41" r:id="rId158"/>
+    <hyperlink ref="J42" r:id="rId159"/>
+    <hyperlink ref="M42" r:id="rId160"/>
+    <hyperlink ref="Q42" r:id="rId161"/>
+    <hyperlink ref="R42" r:id="rId162"/>
+    <hyperlink ref="T42" r:id="rId163"/>
+    <hyperlink ref="J43" r:id="rId164"/>
+    <hyperlink ref="M43" r:id="rId165"/>
+    <hyperlink ref="J44" r:id="rId166"/>
+    <hyperlink ref="M44" r:id="rId167"/>
+    <hyperlink ref="Q44" r:id="rId168"/>
+    <hyperlink ref="R44" r:id="rId169"/>
+    <hyperlink ref="T44" r:id="rId170"/>
+    <hyperlink ref="U44" r:id="rId171"/>
+    <hyperlink ref="M45" r:id="rId172"/>
+    <hyperlink ref="J46" r:id="rId173"/>
+    <hyperlink ref="M46" r:id="rId174"/>
+    <hyperlink ref="T46" r:id="rId175"/>
+    <hyperlink ref="J47" r:id="rId176"/>
+    <hyperlink ref="M47" r:id="rId177"/>
+    <hyperlink ref="Q47" r:id="rId178"/>
+    <hyperlink ref="R47" r:id="rId179"/>
+    <hyperlink ref="J48" r:id="rId180"/>
+    <hyperlink ref="M48" r:id="rId181"/>
+    <hyperlink ref="Q48" r:id="rId182"/>
+    <hyperlink ref="R48" r:id="rId183"/>
+    <hyperlink ref="U48" r:id="rId184"/>
+    <hyperlink ref="J49" r:id="rId185"/>
+    <hyperlink ref="M49" r:id="rId186"/>
+    <hyperlink ref="Q49" r:id="rId187"/>
+    <hyperlink ref="R49" r:id="rId188"/>
+    <hyperlink ref="T49" r:id="rId189"/>
+    <hyperlink ref="J50" r:id="rId190"/>
+    <hyperlink ref="M50" r:id="rId191"/>
+    <hyperlink ref="Q50" r:id="rId192"/>
+    <hyperlink ref="R50" r:id="rId193"/>
+    <hyperlink ref="T50" r:id="rId194"/>
+    <hyperlink ref="M51" r:id="rId195"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
